--- a/data/derived_data/2_RarefyData/ps_rare_ITS_sample_data.xlsx
+++ b/data/derived_data/2_RarefyData/ps_rare_ITS_sample_data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="374">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -662,6 +662,9 @@
     <t xml:space="preserve">MS_120</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_121</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_122</t>
   </si>
   <si>
@@ -920,9 +923,6 @@
     <t xml:space="preserve">MS_204</t>
   </si>
   <si>
-    <t xml:space="preserve">Fruits_5_6days;na</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_207</t>
   </si>
   <si>
@@ -959,6 +959,12 @@
     <t xml:space="preserve">Pupae_Nat_Inf_Focal_Sites</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pupae_Nat_Inf</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_221</t>
   </si>
   <si>
@@ -968,9 +974,6 @@
     <t xml:space="preserve">MS_223</t>
   </si>
   <si>
-    <t xml:space="preserve">Pupae_Nat_Inf</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_224</t>
   </si>
   <si>
@@ -999,6 +1002,9 @@
   </si>
   <si>
     <t xml:space="preserve">MS_233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_234</t>
   </si>
   <si>
     <t xml:space="preserve">MS_235</t>
@@ -8671,7 +8677,7 @@
         <v>210</v>
       </c>
       <c r="F123" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G123" t="s">
         <v>211</v>
@@ -8701,7 +8707,7 @@
         <v>26</v>
       </c>
       <c r="P123" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q123" t="s">
         <v>80</v>
@@ -8751,16 +8757,16 @@
         <v>87</v>
       </c>
       <c r="M124" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N124" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O124" t="s">
         <v>26</v>
       </c>
       <c r="P124" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q124" t="s">
         <v>80</v>
@@ -8819,7 +8825,7 @@
         <v>26</v>
       </c>
       <c r="P125" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q125" t="s">
         <v>80</v>
@@ -8878,7 +8884,7 @@
         <v>26</v>
       </c>
       <c r="P126" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q126" t="s">
         <v>80</v>
@@ -8907,7 +8913,7 @@
         <v>210</v>
       </c>
       <c r="F127" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G127" t="s">
         <v>211</v>
@@ -8922,22 +8928,22 @@
         <v>27</v>
       </c>
       <c r="K127" t="s">
+        <v>43</v>
+      </c>
+      <c r="L127" t="s">
+        <v>87</v>
+      </c>
+      <c r="M127" t="s">
+        <v>88</v>
+      </c>
+      <c r="N127" t="s">
+        <v>89</v>
+      </c>
+      <c r="O127" t="s">
+        <v>26</v>
+      </c>
+      <c r="P127" t="s">
         <v>52</v>
-      </c>
-      <c r="L127" t="s">
-        <v>105</v>
-      </c>
-      <c r="M127" t="s">
-        <v>106</v>
-      </c>
-      <c r="N127" t="s">
-        <v>107</v>
-      </c>
-      <c r="O127" t="s">
-        <v>26</v>
-      </c>
-      <c r="P127" t="s">
-        <v>43</v>
       </c>
       <c r="Q127" t="s">
         <v>80</v>
@@ -8966,7 +8972,7 @@
         <v>210</v>
       </c>
       <c r="F128" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G128" t="s">
         <v>211</v>
@@ -8996,7 +9002,7 @@
         <v>26</v>
       </c>
       <c r="P128" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q128" t="s">
         <v>80</v>
@@ -9043,19 +9049,19 @@
         <v>52</v>
       </c>
       <c r="L129" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="M129" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N129" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O129" t="s">
         <v>26</v>
       </c>
       <c r="P129" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q129" t="s">
         <v>80</v>
@@ -9084,7 +9090,7 @@
         <v>210</v>
       </c>
       <c r="F130" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G130" t="s">
         <v>211</v>
@@ -9114,7 +9120,7 @@
         <v>26</v>
       </c>
       <c r="P130" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q130" t="s">
         <v>80</v>
@@ -9173,7 +9179,7 @@
         <v>26</v>
       </c>
       <c r="P131" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q131" t="s">
         <v>80</v>
@@ -9202,7 +9208,7 @@
         <v>210</v>
       </c>
       <c r="F132" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G132" t="s">
         <v>211</v>
@@ -9211,28 +9217,28 @@
         <v>78</v>
       </c>
       <c r="I132" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J132" t="s">
         <v>27</v>
       </c>
       <c r="K132" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L132" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M132" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="N132" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="O132" t="s">
         <v>26</v>
       </c>
       <c r="P132" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q132" t="s">
         <v>80</v>
@@ -9261,7 +9267,7 @@
         <v>210</v>
       </c>
       <c r="F133" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G133" t="s">
         <v>211</v>
@@ -9291,7 +9297,7 @@
         <v>26</v>
       </c>
       <c r="P133" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q133" t="s">
         <v>80</v>
@@ -9320,7 +9326,7 @@
         <v>210</v>
       </c>
       <c r="F134" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G134" t="s">
         <v>211</v>
@@ -9350,7 +9356,7 @@
         <v>26</v>
       </c>
       <c r="P134" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q134" t="s">
         <v>80</v>
@@ -9394,22 +9400,22 @@
         <v>27</v>
       </c>
       <c r="K135" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L135" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M135" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="N135" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="O135" t="s">
         <v>26</v>
       </c>
       <c r="P135" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="Q135" t="s">
         <v>80</v>
@@ -9468,7 +9474,7 @@
         <v>26</v>
       </c>
       <c r="P136" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q136" t="s">
         <v>80</v>
@@ -9497,7 +9503,7 @@
         <v>210</v>
       </c>
       <c r="F137" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G137" t="s">
         <v>211</v>
@@ -9518,16 +9524,16 @@
         <v>87</v>
       </c>
       <c r="M137" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N137" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O137" t="s">
         <v>26</v>
       </c>
       <c r="P137" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q137" t="s">
         <v>80</v>
@@ -9586,7 +9592,7 @@
         <v>26</v>
       </c>
       <c r="P138" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="Q138" t="s">
         <v>80</v>
@@ -9630,22 +9636,22 @@
         <v>27</v>
       </c>
       <c r="K139" t="s">
+        <v>43</v>
+      </c>
+      <c r="L139" t="s">
+        <v>87</v>
+      </c>
+      <c r="M139" t="s">
+        <v>88</v>
+      </c>
+      <c r="N139" t="s">
+        <v>89</v>
+      </c>
+      <c r="O139" t="s">
+        <v>26</v>
+      </c>
+      <c r="P139" t="s">
         <v>52</v>
-      </c>
-      <c r="L139" t="s">
-        <v>105</v>
-      </c>
-      <c r="M139" t="s">
-        <v>106</v>
-      </c>
-      <c r="N139" t="s">
-        <v>107</v>
-      </c>
-      <c r="O139" t="s">
-        <v>26</v>
-      </c>
-      <c r="P139" t="s">
-        <v>28</v>
       </c>
       <c r="Q139" t="s">
         <v>80</v>
@@ -9674,7 +9680,7 @@
         <v>210</v>
       </c>
       <c r="F140" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G140" t="s">
         <v>211</v>
@@ -9704,7 +9710,7 @@
         <v>26</v>
       </c>
       <c r="P140" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q140" t="s">
         <v>80</v>
@@ -9733,7 +9739,7 @@
         <v>210</v>
       </c>
       <c r="F141" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G141" t="s">
         <v>211</v>
@@ -9763,7 +9769,7 @@
         <v>26</v>
       </c>
       <c r="P141" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q141" t="s">
         <v>80</v>
@@ -9792,7 +9798,7 @@
         <v>210</v>
       </c>
       <c r="F142" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G142" t="s">
         <v>211</v>
@@ -9810,19 +9816,19 @@
         <v>52</v>
       </c>
       <c r="L142" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="M142" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N142" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O142" t="s">
         <v>26</v>
       </c>
       <c r="P142" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q142" t="s">
         <v>80</v>
@@ -9881,7 +9887,7 @@
         <v>26</v>
       </c>
       <c r="P143" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="Q143" t="s">
         <v>80</v>
@@ -9907,46 +9913,46 @@
         <v>36</v>
       </c>
       <c r="E144" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="F144" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G144" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="H144" t="s">
         <v>78</v>
       </c>
       <c r="I144" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="J144" t="s">
         <v>27</v>
       </c>
       <c r="K144" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L144" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M144" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="N144" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="O144" t="s">
         <v>26</v>
       </c>
       <c r="P144" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q144" t="s">
         <v>80</v>
       </c>
       <c r="R144" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="S144" t="s">
         <v>26</v>
@@ -9954,10 +9960,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B145" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C145" t="s">
         <v>20</v>
@@ -9966,13 +9972,13 @@
         <v>36</v>
       </c>
       <c r="E145" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F145" t="s">
         <v>60</v>
       </c>
       <c r="G145" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H145" t="s">
         <v>78</v>
@@ -9999,13 +10005,13 @@
         <v>26</v>
       </c>
       <c r="P145" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q145" t="s">
         <v>80</v>
       </c>
       <c r="R145" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S145" t="s">
         <v>26</v>
@@ -10025,13 +10031,13 @@
         <v>36</v>
       </c>
       <c r="E146" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F146" t="s">
         <v>60</v>
       </c>
       <c r="G146" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H146" t="s">
         <v>78</v>
@@ -10058,13 +10064,13 @@
         <v>26</v>
       </c>
       <c r="P146" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q146" t="s">
         <v>80</v>
       </c>
       <c r="R146" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S146" t="s">
         <v>26</v>
@@ -10084,13 +10090,13 @@
         <v>36</v>
       </c>
       <c r="E147" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F147" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G147" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H147" t="s">
         <v>78</v>
@@ -10102,28 +10108,28 @@
         <v>27</v>
       </c>
       <c r="K147" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L147" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M147" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="N147" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="O147" t="s">
         <v>26</v>
       </c>
       <c r="P147" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="Q147" t="s">
         <v>80</v>
       </c>
       <c r="R147" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S147" t="s">
         <v>26</v>
@@ -10143,13 +10149,13 @@
         <v>36</v>
       </c>
       <c r="E148" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F148" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G148" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H148" t="s">
         <v>78</v>
@@ -10176,13 +10182,13 @@
         <v>26</v>
       </c>
       <c r="P148" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q148" t="s">
         <v>80</v>
       </c>
       <c r="R148" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S148" t="s">
         <v>26</v>
@@ -10202,13 +10208,13 @@
         <v>36</v>
       </c>
       <c r="E149" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F149" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G149" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H149" t="s">
         <v>78</v>
@@ -10226,22 +10232,22 @@
         <v>87</v>
       </c>
       <c r="M149" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N149" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O149" t="s">
         <v>26</v>
       </c>
       <c r="P149" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="Q149" t="s">
         <v>80</v>
       </c>
       <c r="R149" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S149" t="s">
         <v>26</v>
@@ -10261,13 +10267,13 @@
         <v>36</v>
       </c>
       <c r="E150" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F150" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G150" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H150" t="s">
         <v>78</v>
@@ -10294,13 +10300,13 @@
         <v>26</v>
       </c>
       <c r="P150" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q150" t="s">
         <v>80</v>
       </c>
       <c r="R150" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S150" t="s">
         <v>26</v>
@@ -10320,13 +10326,13 @@
         <v>36</v>
       </c>
       <c r="E151" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F151" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G151" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H151" t="s">
         <v>78</v>
@@ -10338,28 +10344,28 @@
         <v>27</v>
       </c>
       <c r="K151" t="s">
+        <v>43</v>
+      </c>
+      <c r="L151" t="s">
+        <v>87</v>
+      </c>
+      <c r="M151" t="s">
+        <v>88</v>
+      </c>
+      <c r="N151" t="s">
+        <v>89</v>
+      </c>
+      <c r="O151" t="s">
+        <v>26</v>
+      </c>
+      <c r="P151" t="s">
         <v>52</v>
-      </c>
-      <c r="L151" t="s">
-        <v>105</v>
-      </c>
-      <c r="M151" t="s">
-        <v>106</v>
-      </c>
-      <c r="N151" t="s">
-        <v>107</v>
-      </c>
-      <c r="O151" t="s">
-        <v>26</v>
-      </c>
-      <c r="P151" t="s">
-        <v>28</v>
       </c>
       <c r="Q151" t="s">
         <v>80</v>
       </c>
       <c r="R151" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S151" t="s">
         <v>26</v>
@@ -10379,13 +10385,13 @@
         <v>36</v>
       </c>
       <c r="E152" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F152" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G152" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H152" t="s">
         <v>78</v>
@@ -10412,13 +10418,13 @@
         <v>26</v>
       </c>
       <c r="P152" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q152" t="s">
         <v>80</v>
       </c>
       <c r="R152" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S152" t="s">
         <v>26</v>
@@ -10438,13 +10444,13 @@
         <v>36</v>
       </c>
       <c r="E153" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F153" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G153" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H153" t="s">
         <v>78</v>
@@ -10471,13 +10477,13 @@
         <v>26</v>
       </c>
       <c r="P153" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q153" t="s">
         <v>80</v>
       </c>
       <c r="R153" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S153" t="s">
         <v>26</v>
@@ -10497,13 +10503,13 @@
         <v>36</v>
       </c>
       <c r="E154" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F154" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G154" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H154" t="s">
         <v>78</v>
@@ -10518,25 +10524,25 @@
         <v>52</v>
       </c>
       <c r="L154" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="M154" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N154" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O154" t="s">
         <v>26</v>
       </c>
       <c r="P154" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q154" t="s">
         <v>80</v>
       </c>
       <c r="R154" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S154" t="s">
         <v>26</v>
@@ -10556,13 +10562,13 @@
         <v>36</v>
       </c>
       <c r="E155" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F155" t="s">
         <v>23</v>
       </c>
       <c r="G155" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H155" t="s">
         <v>78</v>
@@ -10589,13 +10595,13 @@
         <v>26</v>
       </c>
       <c r="P155" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q155" t="s">
         <v>80</v>
       </c>
       <c r="R155" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S155" t="s">
         <v>26</v>
@@ -10615,13 +10621,13 @@
         <v>36</v>
       </c>
       <c r="E156" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F156" t="s">
         <v>23</v>
       </c>
       <c r="G156" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H156" t="s">
         <v>78</v>
@@ -10648,13 +10654,13 @@
         <v>26</v>
       </c>
       <c r="P156" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q156" t="s">
         <v>80</v>
       </c>
       <c r="R156" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S156" t="s">
         <v>26</v>
@@ -10674,46 +10680,46 @@
         <v>36</v>
       </c>
       <c r="E157" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F157" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G157" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H157" t="s">
         <v>78</v>
       </c>
       <c r="I157" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J157" t="s">
         <v>27</v>
       </c>
       <c r="K157" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L157" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M157" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="N157" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="O157" t="s">
         <v>26</v>
       </c>
       <c r="P157" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q157" t="s">
         <v>80</v>
       </c>
       <c r="R157" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S157" t="s">
         <v>26</v>
@@ -10733,13 +10739,13 @@
         <v>36</v>
       </c>
       <c r="E158" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F158" t="s">
         <v>41</v>
       </c>
       <c r="G158" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H158" t="s">
         <v>78</v>
@@ -10766,13 +10772,13 @@
         <v>26</v>
       </c>
       <c r="P158" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q158" t="s">
         <v>80</v>
       </c>
       <c r="R158" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S158" t="s">
         <v>26</v>
@@ -10792,13 +10798,13 @@
         <v>36</v>
       </c>
       <c r="E159" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F159" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G159" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H159" t="s">
         <v>78</v>
@@ -10825,13 +10831,13 @@
         <v>26</v>
       </c>
       <c r="P159" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q159" t="s">
         <v>80</v>
       </c>
       <c r="R159" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S159" t="s">
         <v>26</v>
@@ -10851,13 +10857,13 @@
         <v>36</v>
       </c>
       <c r="E160" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F160" t="s">
         <v>23</v>
       </c>
       <c r="G160" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H160" t="s">
         <v>78</v>
@@ -10869,28 +10875,28 @@
         <v>27</v>
       </c>
       <c r="K160" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L160" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M160" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="N160" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="O160" t="s">
         <v>26</v>
       </c>
       <c r="P160" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="Q160" t="s">
         <v>80</v>
       </c>
       <c r="R160" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S160" t="s">
         <v>26</v>
@@ -10910,13 +10916,13 @@
         <v>36</v>
       </c>
       <c r="E161" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F161" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G161" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H161" t="s">
         <v>78</v>
@@ -10943,13 +10949,13 @@
         <v>26</v>
       </c>
       <c r="P161" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q161" t="s">
         <v>80</v>
       </c>
       <c r="R161" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S161" t="s">
         <v>26</v>
@@ -10969,13 +10975,13 @@
         <v>36</v>
       </c>
       <c r="E162" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F162" t="s">
         <v>41</v>
       </c>
       <c r="G162" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H162" t="s">
         <v>78</v>
@@ -10993,22 +10999,22 @@
         <v>87</v>
       </c>
       <c r="M162" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N162" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O162" t="s">
         <v>26</v>
       </c>
       <c r="P162" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q162" t="s">
         <v>80</v>
       </c>
       <c r="R162" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S162" t="s">
         <v>26</v>
@@ -11028,13 +11034,13 @@
         <v>36</v>
       </c>
       <c r="E163" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F163" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G163" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H163" t="s">
         <v>78</v>
@@ -11061,13 +11067,13 @@
         <v>26</v>
       </c>
       <c r="P163" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q163" t="s">
         <v>80</v>
       </c>
       <c r="R163" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S163" t="s">
         <v>26</v>
@@ -11087,13 +11093,13 @@
         <v>36</v>
       </c>
       <c r="E164" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F164" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G164" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H164" t="s">
         <v>78</v>
@@ -11120,13 +11126,13 @@
         <v>26</v>
       </c>
       <c r="P164" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q164" t="s">
         <v>80</v>
       </c>
       <c r="R164" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S164" t="s">
         <v>26</v>
@@ -11146,13 +11152,13 @@
         <v>36</v>
       </c>
       <c r="E165" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F165" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G165" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H165" t="s">
         <v>78</v>
@@ -11164,28 +11170,28 @@
         <v>27</v>
       </c>
       <c r="K165" t="s">
+        <v>43</v>
+      </c>
+      <c r="L165" t="s">
+        <v>87</v>
+      </c>
+      <c r="M165" t="s">
+        <v>88</v>
+      </c>
+      <c r="N165" t="s">
+        <v>89</v>
+      </c>
+      <c r="O165" t="s">
+        <v>26</v>
+      </c>
+      <c r="P165" t="s">
         <v>52</v>
-      </c>
-      <c r="L165" t="s">
-        <v>105</v>
-      </c>
-      <c r="M165" t="s">
-        <v>106</v>
-      </c>
-      <c r="N165" t="s">
-        <v>107</v>
-      </c>
-      <c r="O165" t="s">
-        <v>26</v>
-      </c>
-      <c r="P165" t="s">
-        <v>28</v>
       </c>
       <c r="Q165" t="s">
         <v>80</v>
       </c>
       <c r="R165" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S165" t="s">
         <v>26</v>
@@ -11205,13 +11211,13 @@
         <v>36</v>
       </c>
       <c r="E166" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F166" t="s">
         <v>23</v>
       </c>
       <c r="G166" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H166" t="s">
         <v>78</v>
@@ -11238,13 +11244,13 @@
         <v>26</v>
       </c>
       <c r="P166" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q166" t="s">
         <v>80</v>
       </c>
       <c r="R166" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S166" t="s">
         <v>26</v>
@@ -11264,13 +11270,13 @@
         <v>36</v>
       </c>
       <c r="E167" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F167" t="s">
         <v>23</v>
       </c>
       <c r="G167" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H167" t="s">
         <v>78</v>
@@ -11297,13 +11303,13 @@
         <v>26</v>
       </c>
       <c r="P167" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q167" t="s">
         <v>80</v>
       </c>
       <c r="R167" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S167" t="s">
         <v>26</v>
@@ -11323,13 +11329,13 @@
         <v>36</v>
       </c>
       <c r="E168" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F168" t="s">
         <v>23</v>
       </c>
       <c r="G168" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H168" t="s">
         <v>78</v>
@@ -11344,25 +11350,25 @@
         <v>52</v>
       </c>
       <c r="L168" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="M168" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N168" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O168" t="s">
         <v>26</v>
       </c>
       <c r="P168" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q168" t="s">
         <v>80</v>
       </c>
       <c r="R168" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S168" t="s">
         <v>26</v>
@@ -11382,13 +11388,13 @@
         <v>36</v>
       </c>
       <c r="E169" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F169" t="s">
         <v>23</v>
       </c>
       <c r="G169" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H169" t="s">
         <v>78</v>
@@ -11415,13 +11421,13 @@
         <v>26</v>
       </c>
       <c r="P169" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q169" t="s">
         <v>80</v>
       </c>
       <c r="R169" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S169" t="s">
         <v>26</v>
@@ -11441,13 +11447,13 @@
         <v>36</v>
       </c>
       <c r="E170" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F170" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G170" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H170" t="s">
         <v>78</v>
@@ -11474,13 +11480,13 @@
         <v>26</v>
       </c>
       <c r="P170" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q170" t="s">
         <v>80</v>
       </c>
       <c r="R170" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S170" t="s">
         <v>26</v>
@@ -11497,63 +11503,63 @@
         <v>20</v>
       </c>
       <c r="D171" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="E171" t="s">
-        <v>22</v>
+        <v>239</v>
       </c>
       <c r="F171" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G171" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="H171" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I171" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="J171" t="s">
         <v>27</v>
       </c>
       <c r="K171" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L171" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M171" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="N171" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="O171" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="P171" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="Q171" t="s">
         <v>80</v>
       </c>
       <c r="R171" t="s">
-        <v>26</v>
+        <v>241</v>
       </c>
       <c r="S171" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B172" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C172" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D172" t="s">
         <v>60</v>
@@ -11565,7 +11571,7 @@
         <v>23</v>
       </c>
       <c r="G172" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H172" t="s">
         <v>25</v>
@@ -11612,19 +11618,19 @@
         <v>270</v>
       </c>
       <c r="C173" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D173" t="s">
         <v>60</v>
       </c>
       <c r="E173" t="s">
-        <v>271</v>
+        <v>22</v>
       </c>
       <c r="F173" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G173" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H173" t="s">
         <v>25</v>
@@ -11636,25 +11642,25 @@
         <v>27</v>
       </c>
       <c r="K173" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L173" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M173" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N173" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="O173" t="s">
-        <v>272</v>
+        <v>32</v>
       </c>
       <c r="P173" t="s">
         <v>26</v>
       </c>
       <c r="Q173" t="s">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="R173" t="s">
         <v>26</v>
@@ -11665,25 +11671,25 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B174" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C174" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D174" t="s">
         <v>60</v>
       </c>
       <c r="E174" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F174" t="s">
         <v>41</v>
       </c>
       <c r="G174" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H174" t="s">
         <v>25</v>
@@ -11707,13 +11713,13 @@
         <v>89</v>
       </c>
       <c r="O174" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P174" t="s">
         <v>26</v>
       </c>
       <c r="Q174" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R174" t="s">
         <v>26</v>
@@ -11730,19 +11736,19 @@
         <v>275</v>
       </c>
       <c r="C175" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D175" t="s">
         <v>60</v>
       </c>
       <c r="E175" t="s">
-        <v>22</v>
+        <v>272</v>
       </c>
       <c r="F175" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G175" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H175" t="s">
         <v>25</v>
@@ -11760,19 +11766,19 @@
         <v>87</v>
       </c>
       <c r="M175" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N175" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="O175" t="s">
-        <v>32</v>
+        <v>273</v>
       </c>
       <c r="P175" t="s">
         <v>26</v>
       </c>
       <c r="Q175" t="s">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="R175" t="s">
         <v>26</v>
@@ -11789,7 +11795,7 @@
         <v>276</v>
       </c>
       <c r="C176" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D176" t="s">
         <v>60</v>
@@ -11801,7 +11807,7 @@
         <v>23</v>
       </c>
       <c r="G176" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H176" t="s">
         <v>25</v>
@@ -11848,7 +11854,7 @@
         <v>277</v>
       </c>
       <c r="C177" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D177" t="s">
         <v>60</v>
@@ -11857,10 +11863,10 @@
         <v>22</v>
       </c>
       <c r="F177" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G177" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H177" t="s">
         <v>25</v>
@@ -11875,13 +11881,13 @@
         <v>43</v>
       </c>
       <c r="L177" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="M177" t="s">
         <v>97</v>
       </c>
       <c r="N177" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O177" t="s">
         <v>32</v>
@@ -11890,7 +11896,7 @@
         <v>26</v>
       </c>
       <c r="Q177" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="R177" t="s">
         <v>26</v>
@@ -11907,7 +11913,7 @@
         <v>278</v>
       </c>
       <c r="C178" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D178" t="s">
         <v>60</v>
@@ -11919,7 +11925,7 @@
         <v>36</v>
       </c>
       <c r="G178" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H178" t="s">
         <v>25</v>
@@ -11966,7 +11972,7 @@
         <v>279</v>
       </c>
       <c r="C179" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D179" t="s">
         <v>60</v>
@@ -11975,10 +11981,10 @@
         <v>22</v>
       </c>
       <c r="F179" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G179" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H179" t="s">
         <v>25</v>
@@ -11990,16 +11996,16 @@
         <v>27</v>
       </c>
       <c r="K179" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L179" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="M179" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="N179" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="O179" t="s">
         <v>32</v>
@@ -12008,7 +12014,7 @@
         <v>26</v>
       </c>
       <c r="Q179" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="R179" t="s">
         <v>26</v>
@@ -12025,7 +12031,7 @@
         <v>280</v>
       </c>
       <c r="C180" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D180" t="s">
         <v>60</v>
@@ -12037,7 +12043,7 @@
         <v>23</v>
       </c>
       <c r="G180" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H180" t="s">
         <v>25</v>
@@ -12084,7 +12090,7 @@
         <v>281</v>
       </c>
       <c r="C181" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D181" t="s">
         <v>60</v>
@@ -12096,7 +12102,7 @@
         <v>23</v>
       </c>
       <c r="G181" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H181" t="s">
         <v>25</v>
@@ -12111,13 +12117,13 @@
         <v>52</v>
       </c>
       <c r="L181" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M181" t="s">
         <v>106</v>
       </c>
       <c r="N181" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="O181" t="s">
         <v>32</v>
@@ -12126,7 +12132,7 @@
         <v>26</v>
       </c>
       <c r="Q181" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="R181" t="s">
         <v>26</v>
@@ -12143,7 +12149,7 @@
         <v>282</v>
       </c>
       <c r="C182" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D182" t="s">
         <v>60</v>
@@ -12155,7 +12161,7 @@
         <v>23</v>
       </c>
       <c r="G182" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H182" t="s">
         <v>25</v>
@@ -12202,7 +12208,7 @@
         <v>283</v>
       </c>
       <c r="C183" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D183" t="s">
         <v>60</v>
@@ -12214,7 +12220,7 @@
         <v>23</v>
       </c>
       <c r="G183" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H183" t="s">
         <v>25</v>
@@ -12229,13 +12235,13 @@
         <v>52</v>
       </c>
       <c r="L183" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="M183" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N183" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="O183" t="s">
         <v>32</v>
@@ -12244,7 +12250,7 @@
         <v>26</v>
       </c>
       <c r="Q183" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="R183" t="s">
         <v>26</v>
@@ -12261,7 +12267,7 @@
         <v>284</v>
       </c>
       <c r="C184" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D184" t="s">
         <v>60</v>
@@ -12273,7 +12279,7 @@
         <v>23</v>
       </c>
       <c r="G184" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H184" t="s">
         <v>25</v>
@@ -12320,7 +12326,7 @@
         <v>285</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D185" t="s">
         <v>60</v>
@@ -12332,7 +12338,7 @@
         <v>23</v>
       </c>
       <c r="G185" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H185" t="s">
         <v>25</v>
@@ -12344,16 +12350,16 @@
         <v>27</v>
       </c>
       <c r="K185" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L185" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M185" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="N185" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="O185" t="s">
         <v>32</v>
@@ -12379,7 +12385,7 @@
         <v>286</v>
       </c>
       <c r="C186" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D186" t="s">
         <v>60</v>
@@ -12391,7 +12397,7 @@
         <v>23</v>
       </c>
       <c r="G186" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H186" t="s">
         <v>25</v>
@@ -12438,19 +12444,19 @@
         <v>287</v>
       </c>
       <c r="C187" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D187" t="s">
         <v>60</v>
       </c>
       <c r="E187" t="s">
-        <v>271</v>
+        <v>22</v>
       </c>
       <c r="F187" t="s">
         <v>23</v>
       </c>
       <c r="G187" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H187" t="s">
         <v>25</v>
@@ -12462,25 +12468,25 @@
         <v>27</v>
       </c>
       <c r="K187" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L187" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M187" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N187" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="O187" t="s">
-        <v>272</v>
+        <v>32</v>
       </c>
       <c r="P187" t="s">
         <v>26</v>
       </c>
       <c r="Q187" t="s">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="R187" t="s">
         <v>26</v>
@@ -12497,19 +12503,19 @@
         <v>288</v>
       </c>
       <c r="C188" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D188" t="s">
         <v>60</v>
       </c>
       <c r="E188" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F188" t="s">
         <v>23</v>
       </c>
       <c r="G188" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H188" t="s">
         <v>25</v>
@@ -12533,13 +12539,13 @@
         <v>89</v>
       </c>
       <c r="O188" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P188" t="s">
         <v>26</v>
       </c>
       <c r="Q188" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R188" t="s">
         <v>26</v>
@@ -12556,19 +12562,19 @@
         <v>289</v>
       </c>
       <c r="C189" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D189" t="s">
         <v>60</v>
       </c>
       <c r="E189" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F189" t="s">
         <v>23</v>
       </c>
       <c r="G189" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H189" t="s">
         <v>25</v>
@@ -12583,22 +12589,22 @@
         <v>43</v>
       </c>
       <c r="L189" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M189" t="s">
         <v>88</v>
       </c>
       <c r="N189" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O189" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P189" t="s">
         <v>26</v>
       </c>
       <c r="Q189" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="R189" t="s">
         <v>26</v>
@@ -12609,25 +12615,25 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B190" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C190" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D190" t="s">
         <v>60</v>
       </c>
       <c r="E190" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F190" t="s">
         <v>23</v>
       </c>
       <c r="G190" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H190" t="s">
         <v>25</v>
@@ -12651,13 +12657,13 @@
         <v>93</v>
       </c>
       <c r="O190" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P190" t="s">
         <v>26</v>
       </c>
       <c r="Q190" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R190" t="s">
         <v>26</v>
@@ -12674,19 +12680,19 @@
         <v>292</v>
       </c>
       <c r="C191" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D191" t="s">
         <v>60</v>
       </c>
       <c r="E191" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F191" t="s">
         <v>23</v>
       </c>
       <c r="G191" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H191" t="s">
         <v>25</v>
@@ -12701,22 +12707,22 @@
         <v>43</v>
       </c>
       <c r="L191" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M191" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N191" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="O191" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P191" t="s">
         <v>26</v>
       </c>
       <c r="Q191" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="R191" t="s">
         <v>26</v>
@@ -12733,19 +12739,19 @@
         <v>293</v>
       </c>
       <c r="C192" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D192" t="s">
         <v>60</v>
       </c>
       <c r="E192" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F192" t="s">
         <v>23</v>
       </c>
       <c r="G192" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H192" t="s">
         <v>25</v>
@@ -12769,13 +12775,13 @@
         <v>98</v>
       </c>
       <c r="O192" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P192" t="s">
         <v>26</v>
       </c>
       <c r="Q192" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R192" t="s">
         <v>26</v>
@@ -12792,19 +12798,19 @@
         <v>294</v>
       </c>
       <c r="C193" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D193" t="s">
         <v>60</v>
       </c>
       <c r="E193" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F193" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G193" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H193" t="s">
         <v>25</v>
@@ -12819,22 +12825,22 @@
         <v>43</v>
       </c>
       <c r="L193" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="M193" t="s">
         <v>97</v>
       </c>
       <c r="N193" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O193" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P193" t="s">
         <v>26</v>
       </c>
       <c r="Q193" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="R193" t="s">
         <v>26</v>
@@ -12851,19 +12857,19 @@
         <v>295</v>
       </c>
       <c r="C194" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D194" t="s">
         <v>60</v>
       </c>
       <c r="E194" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F194" t="s">
         <v>60</v>
       </c>
       <c r="G194" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H194" t="s">
         <v>25</v>
@@ -12887,13 +12893,13 @@
         <v>102</v>
       </c>
       <c r="O194" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P194" t="s">
         <v>26</v>
       </c>
       <c r="Q194" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R194" t="s">
         <v>26</v>
@@ -12910,19 +12916,19 @@
         <v>296</v>
       </c>
       <c r="C195" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D195" t="s">
         <v>60</v>
       </c>
       <c r="E195" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F195" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G195" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H195" t="s">
         <v>25</v>
@@ -12934,25 +12940,25 @@
         <v>27</v>
       </c>
       <c r="K195" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L195" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="M195" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="N195" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="O195" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P195" t="s">
         <v>26</v>
       </c>
       <c r="Q195" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R195" t="s">
         <v>26</v>
@@ -12969,19 +12975,19 @@
         <v>297</v>
       </c>
       <c r="C196" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D196" t="s">
         <v>60</v>
       </c>
       <c r="E196" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F196" t="s">
         <v>41</v>
       </c>
       <c r="G196" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H196" t="s">
         <v>25</v>
@@ -13005,13 +13011,13 @@
         <v>111</v>
       </c>
       <c r="O196" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P196" t="s">
         <v>26</v>
       </c>
       <c r="Q196" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R196" t="s">
         <v>26</v>
@@ -13028,19 +13034,19 @@
         <v>298</v>
       </c>
       <c r="C197" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D197" t="s">
         <v>60</v>
       </c>
       <c r="E197" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F197" t="s">
         <v>41</v>
       </c>
       <c r="G197" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H197" t="s">
         <v>25</v>
@@ -13055,22 +13061,22 @@
         <v>52</v>
       </c>
       <c r="L197" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="M197" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N197" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="O197" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P197" t="s">
         <v>26</v>
       </c>
       <c r="Q197" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="R197" t="s">
         <v>26</v>
@@ -13087,19 +13093,19 @@
         <v>299</v>
       </c>
       <c r="C198" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D198" t="s">
         <v>60</v>
       </c>
       <c r="E198" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F198" t="s">
         <v>41</v>
       </c>
       <c r="G198" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H198" t="s">
         <v>25</v>
@@ -13123,13 +13129,13 @@
         <v>119</v>
       </c>
       <c r="O198" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P198" t="s">
         <v>26</v>
       </c>
       <c r="Q198" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R198" t="s">
         <v>26</v>
@@ -13146,19 +13152,19 @@
         <v>300</v>
       </c>
       <c r="C199" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D199" t="s">
         <v>60</v>
       </c>
       <c r="E199" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F199" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G199" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H199" t="s">
         <v>25</v>
@@ -13173,22 +13179,22 @@
         <v>52</v>
       </c>
       <c r="L199" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="M199" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="N199" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O199" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P199" t="s">
         <v>26</v>
       </c>
       <c r="Q199" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R199" t="s">
         <v>26</v>
@@ -13205,19 +13211,19 @@
         <v>301</v>
       </c>
       <c r="C200" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D200" t="s">
         <v>60</v>
       </c>
       <c r="E200" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F200" t="s">
         <v>36</v>
       </c>
       <c r="G200" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H200" t="s">
         <v>25</v>
@@ -13241,45 +13247,45 @@
         <v>107</v>
       </c>
       <c r="O200" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P200" t="s">
         <v>26</v>
       </c>
       <c r="Q200" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R200" t="s">
         <v>26</v>
       </c>
       <c r="S200" t="s">
-        <v>302</v>
+        <v>34</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B201" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C201" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D201" t="s">
         <v>60</v>
       </c>
       <c r="E201" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="F201" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G201" t="s">
-        <v>183</v>
+        <v>269</v>
       </c>
       <c r="H201" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I201" t="s">
         <v>26</v>
@@ -13288,39 +13294,39 @@
         <v>27</v>
       </c>
       <c r="K201" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L201" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="M201" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="N201" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="O201" t="s">
-        <v>26</v>
+        <v>273</v>
       </c>
       <c r="P201" t="s">
         <v>26</v>
       </c>
       <c r="Q201" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="R201" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="S201" t="s">
-        <v>184</v>
+        <v>34</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B202" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C202" t="s">
         <v>20</v>
@@ -13350,13 +13356,13 @@
         <v>43</v>
       </c>
       <c r="L202" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M202" t="s">
         <v>88</v>
       </c>
       <c r="N202" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O202" t="s">
         <v>26</v>
@@ -13365,7 +13371,7 @@
         <v>26</v>
       </c>
       <c r="Q202" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="R202" t="s">
         <v>184</v>
@@ -13376,13 +13382,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B203" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C203" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D203" t="s">
         <v>60</v>
@@ -13435,13 +13441,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B204" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C204" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D204" t="s">
         <v>60</v>
@@ -13450,7 +13456,7 @@
         <v>304</v>
       </c>
       <c r="F204" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G204" t="s">
         <v>183</v>
@@ -13468,13 +13474,13 @@
         <v>43</v>
       </c>
       <c r="L204" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="M204" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N204" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="O204" t="s">
         <v>26</v>
@@ -13494,13 +13500,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B205" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C205" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D205" t="s">
         <v>60</v>
@@ -13553,13 +13559,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B206" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C206" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D206" t="s">
         <v>60</v>
@@ -13583,16 +13589,16 @@
         <v>27</v>
       </c>
       <c r="K206" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L206" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="M206" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="N206" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="O206" t="s">
         <v>26</v>
@@ -13601,7 +13607,7 @@
         <v>26</v>
       </c>
       <c r="Q206" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="R206" t="s">
         <v>184</v>
@@ -13612,10 +13618,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B207" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C207" t="s">
         <v>20</v>
@@ -13624,13 +13630,13 @@
         <v>60</v>
       </c>
       <c r="E207" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="F207" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G207" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="H207" t="s">
         <v>78</v>
@@ -13642,16 +13648,16 @@
         <v>27</v>
       </c>
       <c r="K207" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L207" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="M207" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="N207" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="O207" t="s">
         <v>26</v>
@@ -13660,21 +13666,21 @@
         <v>26</v>
       </c>
       <c r="Q207" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="R207" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="S207" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B208" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C208" t="s">
         <v>20</v>
@@ -13686,7 +13692,7 @@
         <v>313</v>
       </c>
       <c r="F208" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G208" t="s">
         <v>211</v>
@@ -13707,10 +13713,10 @@
         <v>87</v>
       </c>
       <c r="M208" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N208" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O208" t="s">
         <v>26</v>
@@ -13730,13 +13736,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B209" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C209" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D209" t="s">
         <v>60</v>
@@ -13745,7 +13751,7 @@
         <v>313</v>
       </c>
       <c r="F209" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G209" t="s">
         <v>211</v>
@@ -13763,13 +13769,13 @@
         <v>43</v>
       </c>
       <c r="L209" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="M209" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N209" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="O209" t="s">
         <v>26</v>
@@ -13778,7 +13784,7 @@
         <v>26</v>
       </c>
       <c r="Q209" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="R209" t="s">
         <v>212</v>
@@ -13822,13 +13828,13 @@
         <v>43</v>
       </c>
       <c r="L210" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M210" t="s">
         <v>88</v>
       </c>
       <c r="N210" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O210" t="s">
         <v>26</v>
@@ -13837,7 +13843,7 @@
         <v>26</v>
       </c>
       <c r="Q210" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="R210" t="s">
         <v>212</v>
@@ -13848,10 +13854,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B211" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C211" t="s">
         <v>36</v>
@@ -13881,13 +13887,13 @@
         <v>43</v>
       </c>
       <c r="L211" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M211" t="s">
         <v>88</v>
       </c>
       <c r="N211" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O211" t="s">
         <v>26</v>
@@ -13896,7 +13902,7 @@
         <v>26</v>
       </c>
       <c r="Q211" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="R211" t="s">
         <v>212</v>
@@ -13907,10 +13913,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B212" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C212" t="s">
         <v>20</v>
@@ -13922,7 +13928,7 @@
         <v>313</v>
       </c>
       <c r="F212" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G212" t="s">
         <v>211</v>
@@ -13937,16 +13943,16 @@
         <v>27</v>
       </c>
       <c r="K212" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L212" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="M212" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N212" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="O212" t="s">
         <v>26</v>
@@ -13955,7 +13961,7 @@
         <v>26</v>
       </c>
       <c r="Q212" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="R212" t="s">
         <v>212</v>
@@ -13966,10 +13972,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B213" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C213" t="s">
         <v>36</v>
@@ -13981,7 +13987,7 @@
         <v>313</v>
       </c>
       <c r="F213" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G213" t="s">
         <v>211</v>
@@ -13996,16 +14002,16 @@
         <v>27</v>
       </c>
       <c r="K213" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L213" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="M213" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N213" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="O213" t="s">
         <v>26</v>
@@ -14014,7 +14020,7 @@
         <v>26</v>
       </c>
       <c r="Q213" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="R213" t="s">
         <v>212</v>
@@ -14025,10 +14031,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B214" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C214" t="s">
         <v>20</v>
@@ -14058,13 +14064,13 @@
         <v>52</v>
       </c>
       <c r="L214" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="M214" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N214" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="O214" t="s">
         <v>26</v>
@@ -14073,7 +14079,7 @@
         <v>26</v>
       </c>
       <c r="Q214" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="R214" t="s">
         <v>212</v>
@@ -14084,10 +14090,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B215" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C215" t="s">
         <v>36</v>
@@ -14099,7 +14105,7 @@
         <v>313</v>
       </c>
       <c r="F215" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G215" t="s">
         <v>211</v>
@@ -14117,13 +14123,13 @@
         <v>52</v>
       </c>
       <c r="L215" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="M215" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N215" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="O215" t="s">
         <v>26</v>
@@ -14132,7 +14138,7 @@
         <v>26</v>
       </c>
       <c r="Q215" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="R215" t="s">
         <v>212</v>
@@ -14143,58 +14149,58 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B216" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C216" t="s">
         <v>20</v>
       </c>
       <c r="D216" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E216" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="F216" t="s">
         <v>60</v>
       </c>
       <c r="G216" t="s">
-        <v>326</v>
+        <v>211</v>
       </c>
       <c r="H216" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I216" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="J216" t="s">
         <v>27</v>
       </c>
       <c r="K216" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L216" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M216" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="N216" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="O216" t="s">
         <v>26</v>
       </c>
       <c r="P216" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q216" t="s">
-        <v>80</v>
+        <v>314</v>
       </c>
       <c r="R216" t="s">
-        <v>326</v>
+        <v>212</v>
       </c>
       <c r="S216" t="s">
         <v>26</v>
@@ -14202,58 +14208,58 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B217" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C217" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D217" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E217" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="F217" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G217" t="s">
-        <v>326</v>
+        <v>211</v>
       </c>
       <c r="H217" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I217" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="J217" t="s">
         <v>27</v>
       </c>
       <c r="K217" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L217" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M217" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="N217" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="O217" t="s">
         <v>26</v>
       </c>
       <c r="P217" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="Q217" t="s">
-        <v>80</v>
+        <v>314</v>
       </c>
       <c r="R217" t="s">
-        <v>326</v>
+        <v>212</v>
       </c>
       <c r="S217" t="s">
         <v>26</v>
@@ -14261,10 +14267,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B218" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C218" t="s">
         <v>20</v>
@@ -14273,13 +14279,13 @@
         <v>36</v>
       </c>
       <c r="E218" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F218" t="s">
         <v>60</v>
       </c>
       <c r="G218" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H218" t="s">
         <v>25</v>
@@ -14306,13 +14312,13 @@
         <v>26</v>
       </c>
       <c r="P218" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="Q218" t="s">
         <v>80</v>
       </c>
       <c r="R218" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S218" t="s">
         <v>26</v>
@@ -14320,10 +14326,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B219" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C219" t="s">
         <v>20</v>
@@ -14332,13 +14338,13 @@
         <v>36</v>
       </c>
       <c r="E219" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F219" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G219" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H219" t="s">
         <v>25</v>
@@ -14350,16 +14356,16 @@
         <v>27</v>
       </c>
       <c r="K219" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L219" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M219" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="N219" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="O219" t="s">
         <v>26</v>
@@ -14371,7 +14377,7 @@
         <v>80</v>
       </c>
       <c r="R219" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S219" t="s">
         <v>26</v>
@@ -14379,10 +14385,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B220" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C220" t="s">
         <v>20</v>
@@ -14391,13 +14397,13 @@
         <v>36</v>
       </c>
       <c r="E220" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F220" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G220" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H220" t="s">
         <v>25</v>
@@ -14409,16 +14415,16 @@
         <v>27</v>
       </c>
       <c r="K220" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L220" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M220" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="N220" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="O220" t="s">
         <v>26</v>
@@ -14430,7 +14436,7 @@
         <v>80</v>
       </c>
       <c r="R220" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S220" t="s">
         <v>26</v>
@@ -14438,10 +14444,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B221" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C221" t="s">
         <v>20</v>
@@ -14450,13 +14456,13 @@
         <v>36</v>
       </c>
       <c r="E221" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F221" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G221" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H221" t="s">
         <v>25</v>
@@ -14474,10 +14480,10 @@
         <v>87</v>
       </c>
       <c r="M221" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N221" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O221" t="s">
         <v>26</v>
@@ -14489,7 +14495,7 @@
         <v>80</v>
       </c>
       <c r="R221" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S221" t="s">
         <v>26</v>
@@ -14497,10 +14503,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B222" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C222" t="s">
         <v>20</v>
@@ -14509,13 +14515,13 @@
         <v>36</v>
       </c>
       <c r="E222" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F222" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G222" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H222" t="s">
         <v>25</v>
@@ -14533,10 +14539,10 @@
         <v>87</v>
       </c>
       <c r="M222" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N222" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O222" t="s">
         <v>26</v>
@@ -14548,7 +14554,7 @@
         <v>80</v>
       </c>
       <c r="R222" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S222" t="s">
         <v>26</v>
@@ -14556,10 +14562,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B223" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C223" t="s">
         <v>20</v>
@@ -14568,13 +14574,13 @@
         <v>36</v>
       </c>
       <c r="E223" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F223" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G223" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H223" t="s">
         <v>25</v>
@@ -14592,10 +14598,10 @@
         <v>87</v>
       </c>
       <c r="M223" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N223" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O223" t="s">
         <v>26</v>
@@ -14607,7 +14613,7 @@
         <v>80</v>
       </c>
       <c r="R223" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S223" t="s">
         <v>26</v>
@@ -14615,10 +14621,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B224" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C224" t="s">
         <v>20</v>
@@ -14627,13 +14633,13 @@
         <v>36</v>
       </c>
       <c r="E224" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F224" t="s">
         <v>36</v>
       </c>
       <c r="G224" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H224" t="s">
         <v>25</v>
@@ -14645,16 +14651,16 @@
         <v>27</v>
       </c>
       <c r="K224" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L224" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="M224" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N224" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="O224" t="s">
         <v>26</v>
@@ -14666,7 +14672,7 @@
         <v>80</v>
       </c>
       <c r="R224" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S224" t="s">
         <v>26</v>
@@ -14674,10 +14680,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B225" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C225" t="s">
         <v>20</v>
@@ -14686,13 +14692,13 @@
         <v>36</v>
       </c>
       <c r="E225" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F225" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G225" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H225" t="s">
         <v>25</v>
@@ -14704,16 +14710,16 @@
         <v>27</v>
       </c>
       <c r="K225" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L225" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="M225" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N225" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="O225" t="s">
         <v>26</v>
@@ -14725,7 +14731,7 @@
         <v>80</v>
       </c>
       <c r="R225" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S225" t="s">
         <v>26</v>
@@ -14733,10 +14739,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B226" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C226" t="s">
         <v>20</v>
@@ -14745,13 +14751,13 @@
         <v>36</v>
       </c>
       <c r="E226" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F226" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G226" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H226" t="s">
         <v>25</v>
@@ -14763,16 +14769,16 @@
         <v>27</v>
       </c>
       <c r="K226" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L226" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="M226" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N226" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="O226" t="s">
         <v>26</v>
@@ -14784,7 +14790,7 @@
         <v>80</v>
       </c>
       <c r="R226" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S226" t="s">
         <v>26</v>
@@ -14792,10 +14798,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B227" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C227" t="s">
         <v>20</v>
@@ -14804,13 +14810,13 @@
         <v>36</v>
       </c>
       <c r="E227" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F227" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G227" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H227" t="s">
         <v>25</v>
@@ -14825,13 +14831,13 @@
         <v>52</v>
       </c>
       <c r="L227" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="M227" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N227" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O227" t="s">
         <v>26</v>
@@ -14843,7 +14849,7 @@
         <v>80</v>
       </c>
       <c r="R227" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S227" t="s">
         <v>26</v>
@@ -14851,10 +14857,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B228" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C228" t="s">
         <v>20</v>
@@ -14863,13 +14869,13 @@
         <v>36</v>
       </c>
       <c r="E228" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F228" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G228" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H228" t="s">
         <v>25</v>
@@ -14884,13 +14890,13 @@
         <v>52</v>
       </c>
       <c r="L228" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="M228" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N228" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O228" t="s">
         <v>26</v>
@@ -14902,7 +14908,7 @@
         <v>80</v>
       </c>
       <c r="R228" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S228" t="s">
         <v>26</v>
@@ -14910,10 +14916,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B229" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C229" t="s">
         <v>20</v>
@@ -14922,13 +14928,13 @@
         <v>36</v>
       </c>
       <c r="E229" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F229" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G229" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H229" t="s">
         <v>25</v>
@@ -14943,13 +14949,13 @@
         <v>52</v>
       </c>
       <c r="L229" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="M229" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N229" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O229" t="s">
         <v>26</v>
@@ -14961,7 +14967,7 @@
         <v>80</v>
       </c>
       <c r="R229" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S229" t="s">
         <v>26</v>
@@ -14969,10 +14975,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B230" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C230" t="s">
         <v>20</v>
@@ -14981,46 +14987,46 @@
         <v>36</v>
       </c>
       <c r="E230" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F230" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G230" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H230" t="s">
         <v>25</v>
       </c>
       <c r="I230" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J230" t="s">
         <v>27</v>
       </c>
       <c r="K230" t="s">
+        <v>52</v>
+      </c>
+      <c r="L230" t="s">
+        <v>57</v>
+      </c>
+      <c r="M230" t="s">
+        <v>115</v>
+      </c>
+      <c r="N230" t="s">
+        <v>119</v>
+      </c>
+      <c r="O230" t="s">
+        <v>26</v>
+      </c>
+      <c r="P230" t="s">
         <v>28</v>
-      </c>
-      <c r="L230" t="s">
-        <v>29</v>
-      </c>
-      <c r="M230" t="s">
-        <v>83</v>
-      </c>
-      <c r="N230" t="s">
-        <v>84</v>
-      </c>
-      <c r="O230" t="s">
-        <v>26</v>
-      </c>
-      <c r="P230" t="s">
-        <v>43</v>
       </c>
       <c r="Q230" t="s">
         <v>80</v>
       </c>
       <c r="R230" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S230" t="s">
         <v>26</v>
@@ -15028,10 +15034,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B231" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C231" t="s">
         <v>20</v>
@@ -15040,46 +15046,46 @@
         <v>36</v>
       </c>
       <c r="E231" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F231" t="s">
         <v>23</v>
       </c>
       <c r="G231" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H231" t="s">
         <v>25</v>
       </c>
       <c r="I231" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J231" t="s">
         <v>27</v>
       </c>
       <c r="K231" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L231" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M231" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="N231" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="O231" t="s">
         <v>26</v>
       </c>
       <c r="P231" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q231" t="s">
         <v>80</v>
       </c>
       <c r="R231" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S231" t="s">
         <v>26</v>
@@ -15087,10 +15093,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B232" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C232" t="s">
         <v>20</v>
@@ -15099,46 +15105,46 @@
         <v>36</v>
       </c>
       <c r="E232" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F232" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G232" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H232" t="s">
         <v>25</v>
       </c>
       <c r="I232" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J232" t="s">
         <v>27</v>
       </c>
       <c r="K232" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L232" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="M232" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="N232" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="O232" t="s">
         <v>26</v>
       </c>
       <c r="P232" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q232" t="s">
         <v>80</v>
       </c>
       <c r="R232" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S232" t="s">
         <v>26</v>
@@ -15146,10 +15152,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B233" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C233" t="s">
         <v>20</v>
@@ -15158,13 +15164,13 @@
         <v>36</v>
       </c>
       <c r="E233" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F233" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G233" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H233" t="s">
         <v>25</v>
@@ -15176,16 +15182,16 @@
         <v>27</v>
       </c>
       <c r="K233" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L233" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M233" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="N233" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="O233" t="s">
         <v>26</v>
@@ -15197,7 +15203,7 @@
         <v>80</v>
       </c>
       <c r="R233" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S233" t="s">
         <v>26</v>
@@ -15205,10 +15211,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B234" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C234" t="s">
         <v>20</v>
@@ -15217,13 +15223,13 @@
         <v>36</v>
       </c>
       <c r="E234" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F234" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G234" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H234" t="s">
         <v>25</v>
@@ -15235,16 +15241,16 @@
         <v>27</v>
       </c>
       <c r="K234" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L234" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="M234" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="N234" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="O234" t="s">
         <v>26</v>
@@ -15256,7 +15262,7 @@
         <v>80</v>
       </c>
       <c r="R234" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S234" t="s">
         <v>26</v>
@@ -15264,10 +15270,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B235" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C235" t="s">
         <v>20</v>
@@ -15276,13 +15282,13 @@
         <v>36</v>
       </c>
       <c r="E235" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F235" t="s">
         <v>41</v>
       </c>
       <c r="G235" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H235" t="s">
         <v>25</v>
@@ -15300,10 +15306,10 @@
         <v>87</v>
       </c>
       <c r="M235" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N235" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O235" t="s">
         <v>26</v>
@@ -15315,7 +15321,7 @@
         <v>80</v>
       </c>
       <c r="R235" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S235" t="s">
         <v>26</v>
@@ -15323,10 +15329,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B236" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C236" t="s">
         <v>20</v>
@@ -15335,13 +15341,13 @@
         <v>36</v>
       </c>
       <c r="E236" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F236" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G236" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H236" t="s">
         <v>25</v>
@@ -15359,10 +15365,10 @@
         <v>87</v>
       </c>
       <c r="M236" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N236" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O236" t="s">
         <v>26</v>
@@ -15374,7 +15380,7 @@
         <v>80</v>
       </c>
       <c r="R236" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S236" t="s">
         <v>26</v>
@@ -15382,10 +15388,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B237" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C237" t="s">
         <v>20</v>
@@ -15394,13 +15400,13 @@
         <v>36</v>
       </c>
       <c r="E237" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F237" t="s">
         <v>41</v>
       </c>
       <c r="G237" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H237" t="s">
         <v>25</v>
@@ -15418,10 +15424,10 @@
         <v>87</v>
       </c>
       <c r="M237" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N237" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O237" t="s">
         <v>26</v>
@@ -15433,7 +15439,7 @@
         <v>80</v>
       </c>
       <c r="R237" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S237" t="s">
         <v>26</v>
@@ -15441,10 +15447,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B238" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C238" t="s">
         <v>20</v>
@@ -15453,13 +15459,13 @@
         <v>36</v>
       </c>
       <c r="E238" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F238" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G238" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H238" t="s">
         <v>25</v>
@@ -15471,28 +15477,28 @@
         <v>27</v>
       </c>
       <c r="K238" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L238" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="M238" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N238" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="O238" t="s">
         <v>26</v>
       </c>
       <c r="P238" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q238" t="s">
         <v>80</v>
       </c>
       <c r="R238" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S238" t="s">
         <v>26</v>
@@ -15500,10 +15506,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B239" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C239" t="s">
         <v>20</v>
@@ -15512,13 +15518,13 @@
         <v>36</v>
       </c>
       <c r="E239" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F239" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G239" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H239" t="s">
         <v>25</v>
@@ -15530,28 +15536,28 @@
         <v>27</v>
       </c>
       <c r="K239" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L239" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="M239" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N239" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="O239" t="s">
         <v>26</v>
       </c>
       <c r="P239" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q239" t="s">
         <v>80</v>
       </c>
       <c r="R239" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S239" t="s">
         <v>26</v>
@@ -15559,10 +15565,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B240" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C240" t="s">
         <v>20</v>
@@ -15571,13 +15577,13 @@
         <v>36</v>
       </c>
       <c r="E240" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F240" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G240" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H240" t="s">
         <v>25</v>
@@ -15589,28 +15595,28 @@
         <v>27</v>
       </c>
       <c r="K240" t="s">
+        <v>43</v>
+      </c>
+      <c r="L240" t="s">
+        <v>87</v>
+      </c>
+      <c r="M240" t="s">
+        <v>88</v>
+      </c>
+      <c r="N240" t="s">
+        <v>89</v>
+      </c>
+      <c r="O240" t="s">
+        <v>26</v>
+      </c>
+      <c r="P240" t="s">
         <v>52</v>
-      </c>
-      <c r="L240" t="s">
-        <v>57</v>
-      </c>
-      <c r="M240" t="s">
-        <v>115</v>
-      </c>
-      <c r="N240" t="s">
-        <v>119</v>
-      </c>
-      <c r="O240" t="s">
-        <v>26</v>
-      </c>
-      <c r="P240" t="s">
-        <v>28</v>
       </c>
       <c r="Q240" t="s">
         <v>80</v>
       </c>
       <c r="R240" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S240" t="s">
         <v>26</v>
@@ -15618,10 +15624,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B241" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C241" t="s">
         <v>20</v>
@@ -15630,13 +15636,13 @@
         <v>36</v>
       </c>
       <c r="E241" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F241" t="s">
         <v>23</v>
       </c>
       <c r="G241" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H241" t="s">
         <v>25</v>
@@ -15651,13 +15657,13 @@
         <v>52</v>
       </c>
       <c r="L241" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="M241" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N241" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O241" t="s">
         <v>26</v>
@@ -15669,7 +15675,7 @@
         <v>80</v>
       </c>
       <c r="R241" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S241" t="s">
         <v>26</v>
@@ -15677,10 +15683,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B242" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C242" t="s">
         <v>20</v>
@@ -15689,13 +15695,13 @@
         <v>36</v>
       </c>
       <c r="E242" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F242" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G242" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H242" t="s">
         <v>25</v>
@@ -15710,13 +15716,13 @@
         <v>52</v>
       </c>
       <c r="L242" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="M242" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="N242" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O242" t="s">
         <v>26</v>
@@ -15728,7 +15734,7 @@
         <v>80</v>
       </c>
       <c r="R242" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S242" t="s">
         <v>26</v>
@@ -15736,187 +15742,187 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B243" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C243" t="s">
         <v>20</v>
       </c>
       <c r="D243" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E243" t="s">
-        <v>76</v>
+        <v>326</v>
       </c>
       <c r="F243" t="s">
         <v>23</v>
       </c>
       <c r="G243" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="H243" t="s">
-        <v>355</v>
+        <v>25</v>
       </c>
       <c r="I243" t="s">
         <v>79</v>
       </c>
       <c r="J243" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K243" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L243" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="M243" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="N243" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="O243" t="s">
         <v>26</v>
       </c>
       <c r="P243" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q243" t="s">
         <v>80</v>
       </c>
       <c r="R243" t="s">
-        <v>26</v>
+        <v>327</v>
       </c>
       <c r="S243" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B244" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C244" t="s">
         <v>20</v>
       </c>
       <c r="D244" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E244" t="s">
-        <v>122</v>
+        <v>326</v>
       </c>
       <c r="F244" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G244" t="s">
-        <v>123</v>
+        <v>327</v>
       </c>
       <c r="H244" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I244" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="J244" t="s">
         <v>27</v>
       </c>
       <c r="K244" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="L244" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M244" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="N244" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="O244" t="s">
         <v>26</v>
       </c>
       <c r="P244" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="Q244" t="s">
         <v>80</v>
       </c>
       <c r="R244" t="s">
-        <v>123</v>
+        <v>327</v>
       </c>
       <c r="S244" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B245" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C245" t="s">
         <v>20</v>
       </c>
       <c r="D245" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E245" t="s">
-        <v>122</v>
+        <v>326</v>
       </c>
       <c r="F245" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G245" t="s">
-        <v>123</v>
+        <v>327</v>
       </c>
       <c r="H245" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I245" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="J245" t="s">
         <v>27</v>
       </c>
       <c r="K245" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L245" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="M245" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="N245" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="O245" t="s">
         <v>26</v>
       </c>
       <c r="P245" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="Q245" t="s">
         <v>80</v>
       </c>
       <c r="R245" t="s">
-        <v>123</v>
+        <v>327</v>
       </c>
       <c r="S245" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B246" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C246" t="s">
         <v>20</v>
@@ -15925,34 +15931,34 @@
         <v>20</v>
       </c>
       <c r="E246" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="F246" t="s">
         <v>23</v>
       </c>
       <c r="G246" t="s">
-        <v>123</v>
+        <v>356</v>
       </c>
       <c r="H246" t="s">
-        <v>78</v>
+        <v>357</v>
       </c>
       <c r="I246" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="J246" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K246" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="L246" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="M246" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="N246" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="O246" t="s">
         <v>26</v>
@@ -15964,18 +15970,18 @@
         <v>80</v>
       </c>
       <c r="R246" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="S246" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B247" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C247" t="s">
         <v>20</v>
@@ -16002,16 +16008,16 @@
         <v>27</v>
       </c>
       <c r="K247" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="L247" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="M247" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="N247" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="O247" t="s">
         <v>26</v>
@@ -16031,10 +16037,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B248" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C248" t="s">
         <v>20</v>
@@ -16046,7 +16052,7 @@
         <v>122</v>
       </c>
       <c r="F248" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G248" t="s">
         <v>123</v>
@@ -16055,22 +16061,22 @@
         <v>78</v>
       </c>
       <c r="I248" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J248" t="s">
         <v>27</v>
       </c>
       <c r="K248" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="L248" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="M248" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="N248" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="O248" t="s">
         <v>26</v>
@@ -16090,10 +16096,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B249" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C249" t="s">
         <v>20</v>
@@ -16105,7 +16111,7 @@
         <v>122</v>
       </c>
       <c r="F249" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G249" t="s">
         <v>123</v>
@@ -16114,7 +16120,7 @@
         <v>78</v>
       </c>
       <c r="I249" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J249" t="s">
         <v>27</v>
@@ -16149,10 +16155,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B250" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C250" t="s">
         <v>20</v>
@@ -16173,22 +16179,22 @@
         <v>78</v>
       </c>
       <c r="I250" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J250" t="s">
         <v>27</v>
       </c>
       <c r="K250" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L250" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="M250" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="N250" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="O250" t="s">
         <v>26</v>
@@ -16208,10 +16214,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B251" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C251" t="s">
         <v>20</v>
@@ -16223,7 +16229,7 @@
         <v>122</v>
       </c>
       <c r="F251" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G251" t="s">
         <v>123</v>
@@ -16238,16 +16244,16 @@
         <v>27</v>
       </c>
       <c r="K251" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="L251" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="M251" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="N251" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="O251" t="s">
         <v>26</v>
@@ -16267,10 +16273,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B252" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C252" t="s">
         <v>20</v>
@@ -16279,10 +16285,10 @@
         <v>20</v>
       </c>
       <c r="E252" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F252" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G252" t="s">
         <v>123</v>
@@ -16291,22 +16297,22 @@
         <v>78</v>
       </c>
       <c r="I252" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="J252" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="K252" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L252" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="M252" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="N252" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="O252" t="s">
         <v>26</v>
@@ -16315,7 +16321,7 @@
         <v>26</v>
       </c>
       <c r="Q252" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="R252" t="s">
         <v>123</v>
@@ -16326,10 +16332,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B253" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C253" t="s">
         <v>20</v>
@@ -16338,10 +16344,10 @@
         <v>20</v>
       </c>
       <c r="E253" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F253" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G253" t="s">
         <v>123</v>
@@ -16353,19 +16359,19 @@
         <v>79</v>
       </c>
       <c r="J253" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="K253" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="L253" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="M253" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="N253" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="O253" t="s">
         <v>26</v>
@@ -16374,7 +16380,7 @@
         <v>26</v>
       </c>
       <c r="Q253" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="R253" t="s">
         <v>123</v>
@@ -16385,10 +16391,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B254" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C254" t="s">
         <v>20</v>
@@ -16397,10 +16403,10 @@
         <v>20</v>
       </c>
       <c r="E254" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F254" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G254" t="s">
         <v>123</v>
@@ -16412,19 +16418,19 @@
         <v>79</v>
       </c>
       <c r="J254" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="K254" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L254" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="M254" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="N254" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="O254" t="s">
         <v>26</v>
@@ -16433,7 +16439,7 @@
         <v>26</v>
       </c>
       <c r="Q254" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="R254" t="s">
         <v>123</v>
@@ -16444,46 +16450,46 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B255" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C255" t="s">
         <v>20</v>
       </c>
       <c r="D255" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E255" t="s">
-        <v>368</v>
+        <v>140</v>
       </c>
       <c r="F255" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G255" t="s">
-        <v>239</v>
+        <v>123</v>
       </c>
       <c r="H255" t="s">
         <v>78</v>
       </c>
       <c r="I255" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="J255" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="K255" t="s">
         <v>43</v>
       </c>
       <c r="L255" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="M255" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="N255" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="O255" t="s">
         <v>26</v>
@@ -16492,57 +16498,57 @@
         <v>26</v>
       </c>
       <c r="Q255" t="s">
-        <v>369</v>
+        <v>142</v>
       </c>
       <c r="R255" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
       <c r="S255" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B256" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C256" t="s">
         <v>20</v>
       </c>
       <c r="D256" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E256" t="s">
-        <v>368</v>
+        <v>140</v>
       </c>
       <c r="F256" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G256" t="s">
-        <v>239</v>
+        <v>123</v>
       </c>
       <c r="H256" t="s">
         <v>78</v>
       </c>
       <c r="I256" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="J256" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="K256" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L256" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="M256" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="N256" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="O256" t="s">
         <v>26</v>
@@ -16551,71 +16557,248 @@
         <v>26</v>
       </c>
       <c r="Q256" t="s">
-        <v>369</v>
+        <v>142</v>
       </c>
       <c r="R256" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
       <c r="S256" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B257" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C257" t="s">
         <v>20</v>
       </c>
       <c r="D257" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E257" t="s">
-        <v>304</v>
+        <v>140</v>
       </c>
       <c r="F257" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G257" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="H257" t="s">
         <v>78</v>
       </c>
       <c r="I257" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="J257" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="K257" t="s">
+        <v>43</v>
+      </c>
+      <c r="L257" t="s">
+        <v>26</v>
+      </c>
+      <c r="M257" t="s">
+        <v>26</v>
+      </c>
+      <c r="N257" t="s">
+        <v>26</v>
+      </c>
+      <c r="O257" t="s">
+        <v>26</v>
+      </c>
+      <c r="P257" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>142</v>
+      </c>
+      <c r="R257" t="s">
+        <v>123</v>
+      </c>
+      <c r="S257" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>369</v>
+      </c>
+      <c r="B258" t="s">
+        <v>369</v>
+      </c>
+      <c r="C258" t="s">
+        <v>20</v>
+      </c>
+      <c r="D258" t="s">
+        <v>60</v>
+      </c>
+      <c r="E258" t="s">
+        <v>370</v>
+      </c>
+      <c r="F258" t="s">
+        <v>20</v>
+      </c>
+      <c r="G258" t="s">
+        <v>240</v>
+      </c>
+      <c r="H258" t="s">
+        <v>78</v>
+      </c>
+      <c r="I258" t="s">
+        <v>26</v>
+      </c>
+      <c r="J258" t="s">
+        <v>27</v>
+      </c>
+      <c r="K258" t="s">
+        <v>43</v>
+      </c>
+      <c r="L258" t="s">
+        <v>87</v>
+      </c>
+      <c r="M258" t="s">
+        <v>88</v>
+      </c>
+      <c r="N258" t="s">
+        <v>89</v>
+      </c>
+      <c r="O258" t="s">
+        <v>26</v>
+      </c>
+      <c r="P258" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>371</v>
+      </c>
+      <c r="R258" t="s">
+        <v>241</v>
+      </c>
+      <c r="S258" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>372</v>
+      </c>
+      <c r="B259" t="s">
+        <v>372</v>
+      </c>
+      <c r="C259" t="s">
+        <v>20</v>
+      </c>
+      <c r="D259" t="s">
+        <v>60</v>
+      </c>
+      <c r="E259" t="s">
+        <v>370</v>
+      </c>
+      <c r="F259" t="s">
+        <v>20</v>
+      </c>
+      <c r="G259" t="s">
+        <v>240</v>
+      </c>
+      <c r="H259" t="s">
+        <v>78</v>
+      </c>
+      <c r="I259" t="s">
+        <v>26</v>
+      </c>
+      <c r="J259" t="s">
+        <v>27</v>
+      </c>
+      <c r="K259" t="s">
+        <v>43</v>
+      </c>
+      <c r="L259" t="s">
+        <v>87</v>
+      </c>
+      <c r="M259" t="s">
+        <v>88</v>
+      </c>
+      <c r="N259" t="s">
+        <v>89</v>
+      </c>
+      <c r="O259" t="s">
+        <v>26</v>
+      </c>
+      <c r="P259" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>371</v>
+      </c>
+      <c r="R259" t="s">
+        <v>241</v>
+      </c>
+      <c r="S259" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>373</v>
+      </c>
+      <c r="B260" t="s">
+        <v>373</v>
+      </c>
+      <c r="C260" t="s">
+        <v>20</v>
+      </c>
+      <c r="D260" t="s">
+        <v>60</v>
+      </c>
+      <c r="E260" t="s">
+        <v>304</v>
+      </c>
+      <c r="F260" t="s">
+        <v>23</v>
+      </c>
+      <c r="G260" t="s">
+        <v>183</v>
+      </c>
+      <c r="H260" t="s">
+        <v>78</v>
+      </c>
+      <c r="I260" t="s">
+        <v>26</v>
+      </c>
+      <c r="J260" t="s">
+        <v>27</v>
+      </c>
+      <c r="K260" t="s">
         <v>52</v>
       </c>
-      <c r="L257" t="s">
+      <c r="L260" t="s">
         <v>105</v>
       </c>
-      <c r="M257" t="s">
+      <c r="M260" t="s">
         <v>106</v>
       </c>
-      <c r="N257" t="s">
+      <c r="N260" t="s">
         <v>107</v>
       </c>
-      <c r="O257" t="s">
-        <v>26</v>
-      </c>
-      <c r="P257" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q257" t="s">
+      <c r="O260" t="s">
+        <v>26</v>
+      </c>
+      <c r="P260" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q260" t="s">
         <v>305</v>
       </c>
-      <c r="R257" t="s">
+      <c r="R260" t="s">
         <v>184</v>
       </c>
-      <c r="S257" t="s">
+      <c r="S260" t="s">
         <v>184</v>
       </c>
     </row>

--- a/data/derived_data/2_RarefyData/ps_rare_ITS_sample_data.xlsx
+++ b/data/derived_data/2_RarefyData/ps_rare_ITS_sample_data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="372">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -789,9 +789,6 @@
   </si>
   <si>
     <t xml:space="preserve">MS_166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_167</t>
   </si>
   <si>
     <t xml:space="preserve">MS_168</t>
@@ -10601,7 +10598,7 @@
         <v>238</v>
       </c>
       <c r="E164" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F164" t="s">
         <v>239</v>
@@ -10631,7 +10628,7 @@
         <v>25</v>
       </c>
       <c r="O164" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P164" t="s">
         <v>79</v>
@@ -10657,7 +10654,7 @@
         <v>238</v>
       </c>
       <c r="E165" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F165" t="s">
         <v>239</v>
@@ -10672,22 +10669,22 @@
         <v>26</v>
       </c>
       <c r="J165" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K165" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L165" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="M165" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="N165" t="s">
         <v>25</v>
       </c>
       <c r="O165" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="P165" t="s">
         <v>79</v>
@@ -10743,7 +10740,7 @@
         <v>25</v>
       </c>
       <c r="O166" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P166" t="s">
         <v>79</v>
@@ -10799,7 +10796,7 @@
         <v>25</v>
       </c>
       <c r="O167" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P167" t="s">
         <v>79</v>
@@ -10843,19 +10840,19 @@
         <v>51</v>
       </c>
       <c r="K168" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L168" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M168" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="N168" t="s">
         <v>25</v>
       </c>
       <c r="O168" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="P168" t="s">
         <v>79</v>
@@ -10911,7 +10908,7 @@
         <v>25</v>
       </c>
       <c r="O169" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P169" t="s">
         <v>79</v>
@@ -10937,7 +10934,7 @@
         <v>238</v>
       </c>
       <c r="E170" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F170" t="s">
         <v>239</v>
@@ -10967,7 +10964,7 @@
         <v>25</v>
       </c>
       <c r="O170" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P170" t="s">
         <v>79</v>
@@ -10987,60 +10984,60 @@
         <v>19</v>
       </c>
       <c r="C171" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D171" t="s">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="E171" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F171" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="G171" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="H171" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I171" t="s">
         <v>26</v>
       </c>
       <c r="J171" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="K171" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="L171" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="M171" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="N171" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="O171" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="P171" t="s">
         <v>79</v>
       </c>
       <c r="Q171" t="s">
-        <v>240</v>
+        <v>25</v>
       </c>
       <c r="R171" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B172" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C172" t="s">
         <v>59</v>
@@ -11052,7 +11049,7 @@
         <v>22</v>
       </c>
       <c r="F172" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G172" t="s">
         <v>24</v>
@@ -11096,19 +11093,19 @@
         <v>269</v>
       </c>
       <c r="B173" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C173" t="s">
         <v>59</v>
       </c>
       <c r="D173" t="s">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="E173" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F173" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G173" t="s">
         <v>24</v>
@@ -11120,25 +11117,25 @@
         <v>26</v>
       </c>
       <c r="J173" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="K173" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="L173" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="M173" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N173" t="s">
-        <v>31</v>
+        <v>271</v>
       </c>
       <c r="O173" t="s">
         <v>25</v>
       </c>
       <c r="P173" t="s">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="Q173" t="s">
         <v>25</v>
@@ -11149,22 +11146,22 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B174" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C174" t="s">
         <v>59</v>
       </c>
       <c r="D174" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E174" t="s">
         <v>40</v>
       </c>
       <c r="F174" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G174" t="s">
         <v>24</v>
@@ -11188,13 +11185,13 @@
         <v>88</v>
       </c>
       <c r="N174" t="s">
+        <v>271</v>
+      </c>
+      <c r="O174" t="s">
+        <v>25</v>
+      </c>
+      <c r="P174" t="s">
         <v>272</v>
-      </c>
-      <c r="O174" t="s">
-        <v>25</v>
-      </c>
-      <c r="P174" t="s">
-        <v>273</v>
       </c>
       <c r="Q174" t="s">
         <v>25</v>
@@ -11208,19 +11205,19 @@
         <v>274</v>
       </c>
       <c r="B175" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C175" t="s">
         <v>59</v>
       </c>
       <c r="D175" t="s">
-        <v>271</v>
+        <v>21</v>
       </c>
       <c r="E175" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F175" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G175" t="s">
         <v>24</v>
@@ -11238,19 +11235,19 @@
         <v>86</v>
       </c>
       <c r="L175" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="M175" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N175" t="s">
-        <v>272</v>
+        <v>31</v>
       </c>
       <c r="O175" t="s">
         <v>25</v>
       </c>
       <c r="P175" t="s">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="Q175" t="s">
         <v>25</v>
@@ -11264,7 +11261,7 @@
         <v>275</v>
       </c>
       <c r="B176" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C176" t="s">
         <v>59</v>
@@ -11276,7 +11273,7 @@
         <v>22</v>
       </c>
       <c r="F176" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G176" t="s">
         <v>24</v>
@@ -11320,7 +11317,7 @@
         <v>276</v>
       </c>
       <c r="B177" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C177" t="s">
         <v>59</v>
@@ -11329,10 +11326,10 @@
         <v>21</v>
       </c>
       <c r="E177" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G177" t="s">
         <v>24</v>
@@ -11347,13 +11344,13 @@
         <v>42</v>
       </c>
       <c r="K177" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L177" t="s">
         <v>96</v>
       </c>
       <c r="M177" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N177" t="s">
         <v>31</v>
@@ -11362,7 +11359,7 @@
         <v>25</v>
       </c>
       <c r="P177" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="Q177" t="s">
         <v>25</v>
@@ -11376,7 +11373,7 @@
         <v>277</v>
       </c>
       <c r="B178" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C178" t="s">
         <v>59</v>
@@ -11388,7 +11385,7 @@
         <v>35</v>
       </c>
       <c r="F178" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G178" t="s">
         <v>24</v>
@@ -11432,7 +11429,7 @@
         <v>278</v>
       </c>
       <c r="B179" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C179" t="s">
         <v>59</v>
@@ -11441,10 +11438,10 @@
         <v>21</v>
       </c>
       <c r="E179" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F179" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G179" t="s">
         <v>24</v>
@@ -11456,16 +11453,16 @@
         <v>26</v>
       </c>
       <c r="J179" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K179" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L179" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="M179" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="N179" t="s">
         <v>31</v>
@@ -11474,7 +11471,7 @@
         <v>25</v>
       </c>
       <c r="P179" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="Q179" t="s">
         <v>25</v>
@@ -11488,7 +11485,7 @@
         <v>279</v>
       </c>
       <c r="B180" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C180" t="s">
         <v>59</v>
@@ -11500,7 +11497,7 @@
         <v>22</v>
       </c>
       <c r="F180" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G180" t="s">
         <v>24</v>
@@ -11544,7 +11541,7 @@
         <v>280</v>
       </c>
       <c r="B181" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C181" t="s">
         <v>59</v>
@@ -11556,7 +11553,7 @@
         <v>22</v>
       </c>
       <c r="F181" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G181" t="s">
         <v>24</v>
@@ -11571,13 +11568,13 @@
         <v>51</v>
       </c>
       <c r="K181" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L181" t="s">
         <v>105</v>
       </c>
       <c r="M181" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="N181" t="s">
         <v>31</v>
@@ -11586,7 +11583,7 @@
         <v>25</v>
       </c>
       <c r="P181" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="Q181" t="s">
         <v>25</v>
@@ -11600,7 +11597,7 @@
         <v>281</v>
       </c>
       <c r="B182" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C182" t="s">
         <v>59</v>
@@ -11612,7 +11609,7 @@
         <v>22</v>
       </c>
       <c r="F182" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G182" t="s">
         <v>24</v>
@@ -11656,7 +11653,7 @@
         <v>282</v>
       </c>
       <c r="B183" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C183" t="s">
         <v>59</v>
@@ -11668,7 +11665,7 @@
         <v>22</v>
       </c>
       <c r="F183" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G183" t="s">
         <v>24</v>
@@ -11683,13 +11680,13 @@
         <v>51</v>
       </c>
       <c r="K183" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="L183" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M183" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="N183" t="s">
         <v>31</v>
@@ -11698,7 +11695,7 @@
         <v>25</v>
       </c>
       <c r="P183" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="Q183" t="s">
         <v>25</v>
@@ -11712,7 +11709,7 @@
         <v>283</v>
       </c>
       <c r="B184" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C184" t="s">
         <v>59</v>
@@ -11724,7 +11721,7 @@
         <v>22</v>
       </c>
       <c r="F184" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G184" t="s">
         <v>24</v>
@@ -11768,7 +11765,7 @@
         <v>284</v>
       </c>
       <c r="B185" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C185" t="s">
         <v>59</v>
@@ -11780,7 +11777,7 @@
         <v>22</v>
       </c>
       <c r="F185" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G185" t="s">
         <v>24</v>
@@ -11792,16 +11789,16 @@
         <v>26</v>
       </c>
       <c r="J185" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="K185" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="L185" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="M185" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="N185" t="s">
         <v>31</v>
@@ -11824,7 +11821,7 @@
         <v>285</v>
       </c>
       <c r="B186" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C186" t="s">
         <v>59</v>
@@ -11836,7 +11833,7 @@
         <v>22</v>
       </c>
       <c r="F186" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G186" t="s">
         <v>24</v>
@@ -11880,19 +11877,19 @@
         <v>286</v>
       </c>
       <c r="B187" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C187" t="s">
         <v>59</v>
       </c>
       <c r="D187" t="s">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="E187" t="s">
         <v>22</v>
       </c>
       <c r="F187" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G187" t="s">
         <v>24</v>
@@ -11904,25 +11901,25 @@
         <v>26</v>
       </c>
       <c r="J187" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="K187" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="L187" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="M187" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N187" t="s">
-        <v>31</v>
+        <v>271</v>
       </c>
       <c r="O187" t="s">
         <v>25</v>
       </c>
       <c r="P187" t="s">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="Q187" t="s">
         <v>25</v>
@@ -11936,19 +11933,19 @@
         <v>287</v>
       </c>
       <c r="B188" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C188" t="s">
         <v>59</v>
       </c>
       <c r="D188" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E188" t="s">
         <v>22</v>
       </c>
       <c r="F188" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G188" t="s">
         <v>24</v>
@@ -11972,13 +11969,13 @@
         <v>88</v>
       </c>
       <c r="N188" t="s">
+        <v>271</v>
+      </c>
+      <c r="O188" t="s">
+        <v>25</v>
+      </c>
+      <c r="P188" t="s">
         <v>272</v>
-      </c>
-      <c r="O188" t="s">
-        <v>25</v>
-      </c>
-      <c r="P188" t="s">
-        <v>273</v>
       </c>
       <c r="Q188" t="s">
         <v>25</v>
@@ -11992,19 +11989,19 @@
         <v>288</v>
       </c>
       <c r="B189" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C189" t="s">
         <v>59</v>
       </c>
       <c r="D189" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E189" t="s">
         <v>22</v>
       </c>
       <c r="F189" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G189" t="s">
         <v>24</v>
@@ -12019,22 +12016,22 @@
         <v>42</v>
       </c>
       <c r="K189" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="L189" t="s">
         <v>87</v>
       </c>
       <c r="M189" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N189" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O189" t="s">
         <v>25</v>
       </c>
       <c r="P189" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="Q189" t="s">
         <v>25</v>
@@ -12045,22 +12042,22 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B190" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C190" t="s">
         <v>59</v>
       </c>
       <c r="D190" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E190" t="s">
         <v>22</v>
       </c>
       <c r="F190" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G190" t="s">
         <v>24</v>
@@ -12084,13 +12081,13 @@
         <v>92</v>
       </c>
       <c r="N190" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O190" t="s">
         <v>25</v>
       </c>
       <c r="P190" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q190" t="s">
         <v>25</v>
@@ -12104,19 +12101,19 @@
         <v>291</v>
       </c>
       <c r="B191" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C191" t="s">
         <v>59</v>
       </c>
       <c r="D191" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E191" t="s">
         <v>22</v>
       </c>
       <c r="F191" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G191" t="s">
         <v>24</v>
@@ -12131,22 +12128,22 @@
         <v>42</v>
       </c>
       <c r="K191" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L191" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="M191" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N191" t="s">
+        <v>271</v>
+      </c>
+      <c r="O191" t="s">
+        <v>25</v>
+      </c>
+      <c r="P191" t="s">
         <v>272</v>
-      </c>
-      <c r="O191" t="s">
-        <v>25</v>
-      </c>
-      <c r="P191" t="s">
-        <v>290</v>
       </c>
       <c r="Q191" t="s">
         <v>25</v>
@@ -12160,19 +12157,19 @@
         <v>292</v>
       </c>
       <c r="B192" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C192" t="s">
         <v>59</v>
       </c>
       <c r="D192" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E192" t="s">
         <v>22</v>
       </c>
       <c r="F192" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G192" t="s">
         <v>24</v>
@@ -12196,13 +12193,13 @@
         <v>97</v>
       </c>
       <c r="N192" t="s">
+        <v>271</v>
+      </c>
+      <c r="O192" t="s">
+        <v>25</v>
+      </c>
+      <c r="P192" t="s">
         <v>272</v>
-      </c>
-      <c r="O192" t="s">
-        <v>25</v>
-      </c>
-      <c r="P192" t="s">
-        <v>273</v>
       </c>
       <c r="Q192" t="s">
         <v>25</v>
@@ -12216,19 +12213,19 @@
         <v>293</v>
       </c>
       <c r="B193" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C193" t="s">
         <v>59</v>
       </c>
       <c r="D193" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E193" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="F193" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G193" t="s">
         <v>24</v>
@@ -12243,22 +12240,22 @@
         <v>42</v>
       </c>
       <c r="K193" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L193" t="s">
         <v>96</v>
       </c>
       <c r="M193" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N193" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O193" t="s">
         <v>25</v>
       </c>
       <c r="P193" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="Q193" t="s">
         <v>25</v>
@@ -12272,19 +12269,19 @@
         <v>294</v>
       </c>
       <c r="B194" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C194" t="s">
         <v>59</v>
       </c>
       <c r="D194" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E194" t="s">
         <v>59</v>
       </c>
       <c r="F194" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G194" t="s">
         <v>24</v>
@@ -12308,13 +12305,13 @@
         <v>101</v>
       </c>
       <c r="N194" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O194" t="s">
         <v>25</v>
       </c>
       <c r="P194" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q194" t="s">
         <v>25</v>
@@ -12328,19 +12325,19 @@
         <v>295</v>
       </c>
       <c r="B195" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C195" t="s">
         <v>59</v>
       </c>
       <c r="D195" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E195" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F195" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G195" t="s">
         <v>24</v>
@@ -12352,25 +12349,25 @@
         <v>26</v>
       </c>
       <c r="J195" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K195" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="L195" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="M195" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="N195" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O195" t="s">
         <v>25</v>
       </c>
       <c r="P195" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q195" t="s">
         <v>25</v>
@@ -12384,19 +12381,19 @@
         <v>296</v>
       </c>
       <c r="B196" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C196" t="s">
         <v>59</v>
       </c>
       <c r="D196" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E196" t="s">
         <v>40</v>
       </c>
       <c r="F196" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G196" t="s">
         <v>24</v>
@@ -12420,13 +12417,13 @@
         <v>110</v>
       </c>
       <c r="N196" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O196" t="s">
         <v>25</v>
       </c>
       <c r="P196" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q196" t="s">
         <v>25</v>
@@ -12440,19 +12437,19 @@
         <v>297</v>
       </c>
       <c r="B197" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C197" t="s">
         <v>59</v>
       </c>
       <c r="D197" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E197" t="s">
         <v>40</v>
       </c>
       <c r="F197" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G197" t="s">
         <v>24</v>
@@ -12467,22 +12464,22 @@
         <v>51</v>
       </c>
       <c r="K197" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="L197" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M197" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="N197" t="s">
+        <v>271</v>
+      </c>
+      <c r="O197" t="s">
+        <v>25</v>
+      </c>
+      <c r="P197" t="s">
         <v>272</v>
-      </c>
-      <c r="O197" t="s">
-        <v>25</v>
-      </c>
-      <c r="P197" t="s">
-        <v>290</v>
       </c>
       <c r="Q197" t="s">
         <v>25</v>
@@ -12496,19 +12493,19 @@
         <v>298</v>
       </c>
       <c r="B198" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C198" t="s">
         <v>59</v>
       </c>
       <c r="D198" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E198" t="s">
         <v>40</v>
       </c>
       <c r="F198" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G198" t="s">
         <v>24</v>
@@ -12532,13 +12529,13 @@
         <v>118</v>
       </c>
       <c r="N198" t="s">
+        <v>271</v>
+      </c>
+      <c r="O198" t="s">
+        <v>25</v>
+      </c>
+      <c r="P198" t="s">
         <v>272</v>
-      </c>
-      <c r="O198" t="s">
-        <v>25</v>
-      </c>
-      <c r="P198" t="s">
-        <v>273</v>
       </c>
       <c r="Q198" t="s">
         <v>25</v>
@@ -12552,19 +12549,19 @@
         <v>299</v>
       </c>
       <c r="B199" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C199" t="s">
         <v>59</v>
       </c>
       <c r="D199" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E199" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F199" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G199" t="s">
         <v>24</v>
@@ -12579,22 +12576,22 @@
         <v>51</v>
       </c>
       <c r="K199" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="L199" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="M199" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="N199" t="s">
+        <v>271</v>
+      </c>
+      <c r="O199" t="s">
+        <v>25</v>
+      </c>
+      <c r="P199" t="s">
         <v>272</v>
-      </c>
-      <c r="O199" t="s">
-        <v>25</v>
-      </c>
-      <c r="P199" t="s">
-        <v>273</v>
       </c>
       <c r="Q199" t="s">
         <v>25</v>
@@ -12608,19 +12605,19 @@
         <v>300</v>
       </c>
       <c r="B200" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C200" t="s">
         <v>59</v>
       </c>
       <c r="D200" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E200" t="s">
         <v>35</v>
       </c>
       <c r="F200" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G200" t="s">
         <v>24</v>
@@ -12644,13 +12641,13 @@
         <v>106</v>
       </c>
       <c r="N200" t="s">
+        <v>271</v>
+      </c>
+      <c r="O200" t="s">
+        <v>25</v>
+      </c>
+      <c r="P200" t="s">
         <v>272</v>
-      </c>
-      <c r="O200" t="s">
-        <v>25</v>
-      </c>
-      <c r="P200" t="s">
-        <v>273</v>
       </c>
       <c r="Q200" t="s">
         <v>25</v>
@@ -12664,22 +12661,22 @@
         <v>301</v>
       </c>
       <c r="B201" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C201" t="s">
         <v>59</v>
       </c>
       <c r="D201" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="E201" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F201" t="s">
-        <v>268</v>
+        <v>182</v>
       </c>
       <c r="G201" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="H201" t="s">
         <v>25</v>
@@ -12688,36 +12685,36 @@
         <v>26</v>
       </c>
       <c r="J201" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K201" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="L201" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="M201" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N201" t="s">
-        <v>272</v>
+        <v>25</v>
       </c>
       <c r="O201" t="s">
         <v>25</v>
       </c>
       <c r="P201" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="Q201" t="s">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="R201" t="s">
-        <v>33</v>
+        <v>183</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B202" t="s">
         <v>19</v>
@@ -12726,7 +12723,7 @@
         <v>59</v>
       </c>
       <c r="D202" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E202" t="s">
         <v>22</v>
@@ -12747,13 +12744,13 @@
         <v>42</v>
       </c>
       <c r="K202" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="L202" t="s">
         <v>87</v>
       </c>
       <c r="M202" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N202" t="s">
         <v>25</v>
@@ -12762,7 +12759,7 @@
         <v>25</v>
       </c>
       <c r="P202" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q202" t="s">
         <v>183</v>
@@ -12773,16 +12770,16 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B203" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C203" t="s">
         <v>59</v>
       </c>
       <c r="D203" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E203" t="s">
         <v>22</v>
@@ -12818,7 +12815,7 @@
         <v>25</v>
       </c>
       <c r="P203" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q203" t="s">
         <v>183</v>
@@ -12832,16 +12829,16 @@
         <v>307</v>
       </c>
       <c r="B204" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C204" t="s">
         <v>59</v>
       </c>
       <c r="D204" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E204" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F204" t="s">
         <v>182</v>
@@ -12859,13 +12856,13 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L204" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="M204" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="N204" t="s">
         <v>25</v>
@@ -12874,7 +12871,7 @@
         <v>25</v>
       </c>
       <c r="P204" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q204" t="s">
         <v>183</v>
@@ -12888,13 +12885,13 @@
         <v>308</v>
       </c>
       <c r="B205" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C205" t="s">
         <v>59</v>
       </c>
       <c r="D205" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E205" t="s">
         <v>35</v>
@@ -12930,7 +12927,7 @@
         <v>25</v>
       </c>
       <c r="P205" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q205" t="s">
         <v>183</v>
@@ -12944,13 +12941,13 @@
         <v>309</v>
       </c>
       <c r="B206" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C206" t="s">
         <v>59</v>
       </c>
       <c r="D206" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E206" t="s">
         <v>35</v>
@@ -12968,16 +12965,16 @@
         <v>26</v>
       </c>
       <c r="J206" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K206" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="L206" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="M206" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="N206" t="s">
         <v>25</v>
@@ -12986,7 +12983,7 @@
         <v>25</v>
       </c>
       <c r="P206" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="Q206" t="s">
         <v>183</v>
@@ -13006,13 +13003,13 @@
         <v>59</v>
       </c>
       <c r="D207" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="E207" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F207" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="G207" t="s">
         <v>77</v>
@@ -13024,16 +13021,16 @@
         <v>26</v>
       </c>
       <c r="J207" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K207" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="L207" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="M207" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="N207" t="s">
         <v>25</v>
@@ -13042,18 +13039,18 @@
         <v>25</v>
       </c>
       <c r="P207" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="Q207" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="R207" t="s">
-        <v>183</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B208" t="s">
         <v>19</v>
@@ -13062,10 +13059,10 @@
         <v>59</v>
       </c>
       <c r="D208" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E208" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F208" t="s">
         <v>210</v>
@@ -13083,13 +13080,13 @@
         <v>42</v>
       </c>
       <c r="K208" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L208" t="s">
         <v>96</v>
       </c>
       <c r="M208" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N208" t="s">
         <v>25</v>
@@ -13098,7 +13095,7 @@
         <v>25</v>
       </c>
       <c r="P208" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q208" t="s">
         <v>211</v>
@@ -13109,7 +13106,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B209" t="s">
         <v>19</v>
@@ -13118,10 +13115,10 @@
         <v>59</v>
       </c>
       <c r="D209" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E209" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F209" t="s">
         <v>210</v>
@@ -13139,13 +13136,13 @@
         <v>42</v>
       </c>
       <c r="K209" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="L209" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="M209" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="N209" t="s">
         <v>25</v>
@@ -13154,7 +13151,7 @@
         <v>25</v>
       </c>
       <c r="P209" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="Q209" t="s">
         <v>211</v>
@@ -13168,13 +13165,13 @@
         <v>316</v>
       </c>
       <c r="B210" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C210" t="s">
         <v>59</v>
       </c>
       <c r="D210" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E210" t="s">
         <v>22</v>
@@ -13210,7 +13207,7 @@
         <v>25</v>
       </c>
       <c r="P210" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q210" t="s">
         <v>211</v>
@@ -13224,13 +13221,13 @@
         <v>317</v>
       </c>
       <c r="B211" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C211" t="s">
         <v>59</v>
       </c>
       <c r="D211" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E211" t="s">
         <v>22</v>
@@ -13251,13 +13248,13 @@
         <v>42</v>
       </c>
       <c r="K211" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="L211" t="s">
         <v>87</v>
       </c>
       <c r="M211" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N211" t="s">
         <v>25</v>
@@ -13266,7 +13263,7 @@
         <v>25</v>
       </c>
       <c r="P211" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q211" t="s">
         <v>211</v>
@@ -13280,13 +13277,13 @@
         <v>318</v>
       </c>
       <c r="B212" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C212" t="s">
         <v>59</v>
       </c>
       <c r="D212" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E212" t="s">
         <v>22</v>
@@ -13322,7 +13319,7 @@
         <v>25</v>
       </c>
       <c r="P212" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q212" t="s">
         <v>211</v>
@@ -13336,16 +13333,16 @@
         <v>319</v>
       </c>
       <c r="B213" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C213" t="s">
         <v>59</v>
       </c>
       <c r="D213" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E213" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="F213" t="s">
         <v>210</v>
@@ -13360,16 +13357,16 @@
         <v>26</v>
       </c>
       <c r="J213" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K213" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="L213" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="M213" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="N213" t="s">
         <v>25</v>
@@ -13378,7 +13375,7 @@
         <v>25</v>
       </c>
       <c r="P213" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q213" t="s">
         <v>211</v>
@@ -13392,13 +13389,13 @@
         <v>320</v>
       </c>
       <c r="B214" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C214" t="s">
         <v>59</v>
       </c>
       <c r="D214" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E214" t="s">
         <v>59</v>
@@ -13434,7 +13431,7 @@
         <v>25</v>
       </c>
       <c r="P214" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q214" t="s">
         <v>211</v>
@@ -13448,13 +13445,13 @@
         <v>321</v>
       </c>
       <c r="B215" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C215" t="s">
         <v>59</v>
       </c>
       <c r="D215" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E215" t="s">
         <v>59</v>
@@ -13475,13 +13472,13 @@
         <v>51</v>
       </c>
       <c r="K215" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="L215" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M215" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="N215" t="s">
         <v>25</v>
@@ -13490,7 +13487,7 @@
         <v>25</v>
       </c>
       <c r="P215" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="Q215" t="s">
         <v>211</v>
@@ -13504,16 +13501,16 @@
         <v>322</v>
       </c>
       <c r="B216" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C216" t="s">
         <v>59</v>
       </c>
       <c r="D216" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E216" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F216" t="s">
         <v>210</v>
@@ -13546,7 +13543,7 @@
         <v>25</v>
       </c>
       <c r="P216" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q216" t="s">
         <v>211</v>
@@ -13560,52 +13557,52 @@
         <v>323</v>
       </c>
       <c r="B217" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C217" t="s">
+        <v>35</v>
+      </c>
+      <c r="D217" t="s">
+        <v>324</v>
+      </c>
+      <c r="E217" t="s">
         <v>59</v>
       </c>
-      <c r="D217" t="s">
-        <v>312</v>
-      </c>
-      <c r="E217" t="s">
-        <v>35</v>
-      </c>
       <c r="F217" t="s">
-        <v>210</v>
+        <v>325</v>
       </c>
       <c r="G217" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="H217" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="I217" t="s">
         <v>26</v>
       </c>
       <c r="J217" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="K217" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="L217" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="M217" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="N217" t="s">
         <v>25</v>
       </c>
       <c r="O217" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P217" t="s">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="Q217" t="s">
-        <v>211</v>
+        <v>325</v>
       </c>
       <c r="R217" t="s">
         <v>25</v>
@@ -13613,22 +13610,22 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
+        <v>326</v>
+      </c>
+      <c r="B218" t="s">
+        <v>19</v>
+      </c>
+      <c r="C218" t="s">
+        <v>35</v>
+      </c>
+      <c r="D218" t="s">
         <v>324</v>
-      </c>
-      <c r="B218" t="s">
-        <v>19</v>
-      </c>
-      <c r="C218" t="s">
-        <v>35</v>
-      </c>
-      <c r="D218" t="s">
-        <v>325</v>
       </c>
       <c r="E218" t="s">
         <v>59</v>
       </c>
       <c r="F218" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G218" t="s">
         <v>24</v>
@@ -13655,13 +13652,13 @@
         <v>25</v>
       </c>
       <c r="O218" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P218" t="s">
         <v>79</v>
       </c>
       <c r="Q218" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R218" t="s">
         <v>25</v>
@@ -13678,13 +13675,13 @@
         <v>35</v>
       </c>
       <c r="D219" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E219" t="s">
         <v>59</v>
       </c>
       <c r="F219" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G219" t="s">
         <v>24</v>
@@ -13711,13 +13708,13 @@
         <v>25</v>
       </c>
       <c r="O219" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P219" t="s">
         <v>79</v>
       </c>
       <c r="Q219" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R219" t="s">
         <v>25</v>
@@ -13734,13 +13731,13 @@
         <v>35</v>
       </c>
       <c r="D220" t="s">
+        <v>324</v>
+      </c>
+      <c r="E220" t="s">
+        <v>40</v>
+      </c>
+      <c r="F220" t="s">
         <v>325</v>
-      </c>
-      <c r="E220" t="s">
-        <v>59</v>
-      </c>
-      <c r="F220" t="s">
-        <v>326</v>
       </c>
       <c r="G220" t="s">
         <v>24</v>
@@ -13752,28 +13749,28 @@
         <v>26</v>
       </c>
       <c r="J220" t="s">
+        <v>42</v>
+      </c>
+      <c r="K220" t="s">
+        <v>86</v>
+      </c>
+      <c r="L220" t="s">
+        <v>96</v>
+      </c>
+      <c r="M220" t="s">
+        <v>97</v>
+      </c>
+      <c r="N220" t="s">
+        <v>25</v>
+      </c>
+      <c r="O220" t="s">
         <v>27</v>
       </c>
-      <c r="K220" t="s">
-        <v>28</v>
-      </c>
-      <c r="L220" t="s">
-        <v>82</v>
-      </c>
-      <c r="M220" t="s">
-        <v>83</v>
-      </c>
-      <c r="N220" t="s">
-        <v>25</v>
-      </c>
-      <c r="O220" t="s">
-        <v>51</v>
-      </c>
       <c r="P220" t="s">
         <v>79</v>
       </c>
       <c r="Q220" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R220" t="s">
         <v>25</v>
@@ -13790,13 +13787,13 @@
         <v>35</v>
       </c>
       <c r="D221" t="s">
+        <v>324</v>
+      </c>
+      <c r="E221" t="s">
+        <v>22</v>
+      </c>
+      <c r="F221" t="s">
         <v>325</v>
-      </c>
-      <c r="E221" t="s">
-        <v>40</v>
-      </c>
-      <c r="F221" t="s">
-        <v>326</v>
       </c>
       <c r="G221" t="s">
         <v>24</v>
@@ -13823,13 +13820,13 @@
         <v>25</v>
       </c>
       <c r="O221" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P221" t="s">
         <v>79</v>
       </c>
       <c r="Q221" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R221" t="s">
         <v>25</v>
@@ -13846,13 +13843,13 @@
         <v>35</v>
       </c>
       <c r="D222" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E222" t="s">
         <v>22</v>
       </c>
       <c r="F222" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G222" t="s">
         <v>24</v>
@@ -13879,13 +13876,13 @@
         <v>25</v>
       </c>
       <c r="O222" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P222" t="s">
         <v>79</v>
       </c>
       <c r="Q222" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R222" t="s">
         <v>25</v>
@@ -13902,13 +13899,13 @@
         <v>35</v>
       </c>
       <c r="D223" t="s">
+        <v>324</v>
+      </c>
+      <c r="E223" t="s">
+        <v>35</v>
+      </c>
+      <c r="F223" t="s">
         <v>325</v>
-      </c>
-      <c r="E223" t="s">
-        <v>22</v>
-      </c>
-      <c r="F223" t="s">
-        <v>326</v>
       </c>
       <c r="G223" t="s">
         <v>24</v>
@@ -13926,22 +13923,22 @@
         <v>86</v>
       </c>
       <c r="L223" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="M223" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N223" t="s">
         <v>25</v>
       </c>
       <c r="O223" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="P223" t="s">
         <v>79</v>
       </c>
       <c r="Q223" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R223" t="s">
         <v>25</v>
@@ -13958,13 +13955,13 @@
         <v>35</v>
       </c>
       <c r="D224" t="s">
+        <v>324</v>
+      </c>
+      <c r="E224" t="s">
+        <v>59</v>
+      </c>
+      <c r="F224" t="s">
         <v>325</v>
-      </c>
-      <c r="E224" t="s">
-        <v>35</v>
-      </c>
-      <c r="F224" t="s">
-        <v>326</v>
       </c>
       <c r="G224" t="s">
         <v>24</v>
@@ -13991,13 +13988,13 @@
         <v>25</v>
       </c>
       <c r="O224" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P224" t="s">
         <v>79</v>
       </c>
       <c r="Q224" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R224" t="s">
         <v>25</v>
@@ -14014,13 +14011,13 @@
         <v>35</v>
       </c>
       <c r="D225" t="s">
+        <v>324</v>
+      </c>
+      <c r="E225" t="s">
+        <v>35</v>
+      </c>
+      <c r="F225" t="s">
         <v>325</v>
-      </c>
-      <c r="E225" t="s">
-        <v>59</v>
-      </c>
-      <c r="F225" t="s">
-        <v>326</v>
       </c>
       <c r="G225" t="s">
         <v>24</v>
@@ -14047,13 +14044,13 @@
         <v>25</v>
       </c>
       <c r="O225" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P225" t="s">
         <v>79</v>
       </c>
       <c r="Q225" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R225" t="s">
         <v>25</v>
@@ -14070,13 +14067,13 @@
         <v>35</v>
       </c>
       <c r="D226" t="s">
+        <v>324</v>
+      </c>
+      <c r="E226" t="s">
+        <v>35</v>
+      </c>
+      <c r="F226" t="s">
         <v>325</v>
-      </c>
-      <c r="E226" t="s">
-        <v>35</v>
-      </c>
-      <c r="F226" t="s">
-        <v>326</v>
       </c>
       <c r="G226" t="s">
         <v>24</v>
@@ -14088,28 +14085,28 @@
         <v>26</v>
       </c>
       <c r="J226" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K226" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L226" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="M226" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="N226" t="s">
         <v>25</v>
       </c>
       <c r="O226" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="P226" t="s">
         <v>79</v>
       </c>
       <c r="Q226" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R226" t="s">
         <v>25</v>
@@ -14126,13 +14123,13 @@
         <v>35</v>
       </c>
       <c r="D227" t="s">
+        <v>324</v>
+      </c>
+      <c r="E227" t="s">
+        <v>35</v>
+      </c>
+      <c r="F227" t="s">
         <v>325</v>
-      </c>
-      <c r="E227" t="s">
-        <v>35</v>
-      </c>
-      <c r="F227" t="s">
-        <v>326</v>
       </c>
       <c r="G227" t="s">
         <v>24</v>
@@ -14159,13 +14156,13 @@
         <v>25</v>
       </c>
       <c r="O227" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P227" t="s">
         <v>79</v>
       </c>
       <c r="Q227" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R227" t="s">
         <v>25</v>
@@ -14182,13 +14179,13 @@
         <v>35</v>
       </c>
       <c r="D228" t="s">
+        <v>324</v>
+      </c>
+      <c r="E228" t="s">
+        <v>40</v>
+      </c>
+      <c r="F228" t="s">
         <v>325</v>
-      </c>
-      <c r="E228" t="s">
-        <v>35</v>
-      </c>
-      <c r="F228" t="s">
-        <v>326</v>
       </c>
       <c r="G228" t="s">
         <v>24</v>
@@ -14215,13 +14212,13 @@
         <v>25</v>
       </c>
       <c r="O228" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P228" t="s">
         <v>79</v>
       </c>
       <c r="Q228" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R228" t="s">
         <v>25</v>
@@ -14238,13 +14235,13 @@
         <v>35</v>
       </c>
       <c r="D229" t="s">
+        <v>324</v>
+      </c>
+      <c r="E229" t="s">
+        <v>22</v>
+      </c>
+      <c r="F229" t="s">
         <v>325</v>
-      </c>
-      <c r="E229" t="s">
-        <v>40</v>
-      </c>
-      <c r="F229" t="s">
-        <v>326</v>
       </c>
       <c r="G229" t="s">
         <v>24</v>
@@ -14259,25 +14256,25 @@
         <v>51</v>
       </c>
       <c r="K229" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L229" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M229" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="N229" t="s">
         <v>25</v>
       </c>
       <c r="O229" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="P229" t="s">
         <v>79</v>
       </c>
       <c r="Q229" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R229" t="s">
         <v>25</v>
@@ -14294,13 +14291,13 @@
         <v>35</v>
       </c>
       <c r="D230" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E230" t="s">
         <v>22</v>
       </c>
       <c r="F230" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G230" t="s">
         <v>24</v>
@@ -14327,13 +14324,13 @@
         <v>25</v>
       </c>
       <c r="O230" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P230" t="s">
         <v>79</v>
       </c>
       <c r="Q230" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R230" t="s">
         <v>25</v>
@@ -14350,13 +14347,13 @@
         <v>35</v>
       </c>
       <c r="D231" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E231" t="s">
         <v>22</v>
       </c>
       <c r="F231" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G231" t="s">
         <v>24</v>
@@ -14383,13 +14380,13 @@
         <v>25</v>
       </c>
       <c r="O231" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P231" t="s">
         <v>79</v>
       </c>
       <c r="Q231" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R231" t="s">
         <v>25</v>
@@ -14406,46 +14403,46 @@
         <v>35</v>
       </c>
       <c r="D232" t="s">
+        <v>324</v>
+      </c>
+      <c r="E232" t="s">
+        <v>40</v>
+      </c>
+      <c r="F232" t="s">
         <v>325</v>
-      </c>
-      <c r="E232" t="s">
-        <v>22</v>
-      </c>
-      <c r="F232" t="s">
-        <v>326</v>
       </c>
       <c r="G232" t="s">
         <v>24</v>
       </c>
       <c r="H232" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="I232" t="s">
         <v>26</v>
       </c>
       <c r="J232" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="K232" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="L232" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="M232" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="N232" t="s">
         <v>25</v>
       </c>
       <c r="O232" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="P232" t="s">
         <v>79</v>
       </c>
       <c r="Q232" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R232" t="s">
         <v>25</v>
@@ -14462,13 +14459,13 @@
         <v>35</v>
       </c>
       <c r="D233" t="s">
+        <v>324</v>
+      </c>
+      <c r="E233" t="s">
+        <v>22</v>
+      </c>
+      <c r="F233" t="s">
         <v>325</v>
-      </c>
-      <c r="E233" t="s">
-        <v>40</v>
-      </c>
-      <c r="F233" t="s">
-        <v>326</v>
       </c>
       <c r="G233" t="s">
         <v>24</v>
@@ -14495,13 +14492,13 @@
         <v>25</v>
       </c>
       <c r="O233" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P233" t="s">
         <v>79</v>
       </c>
       <c r="Q233" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R233" t="s">
         <v>25</v>
@@ -14518,13 +14515,13 @@
         <v>35</v>
       </c>
       <c r="D234" t="s">
+        <v>324</v>
+      </c>
+      <c r="E234" t="s">
+        <v>40</v>
+      </c>
+      <c r="F234" t="s">
         <v>325</v>
-      </c>
-      <c r="E234" t="s">
-        <v>22</v>
-      </c>
-      <c r="F234" t="s">
-        <v>326</v>
       </c>
       <c r="G234" t="s">
         <v>24</v>
@@ -14536,28 +14533,28 @@
         <v>26</v>
       </c>
       <c r="J234" t="s">
+        <v>42</v>
+      </c>
+      <c r="K234" t="s">
+        <v>86</v>
+      </c>
+      <c r="L234" t="s">
+        <v>96</v>
+      </c>
+      <c r="M234" t="s">
+        <v>97</v>
+      </c>
+      <c r="N234" t="s">
+        <v>25</v>
+      </c>
+      <c r="O234" t="s">
         <v>27</v>
       </c>
-      <c r="K234" t="s">
-        <v>28</v>
-      </c>
-      <c r="L234" t="s">
-        <v>82</v>
-      </c>
-      <c r="M234" t="s">
-        <v>83</v>
-      </c>
-      <c r="N234" t="s">
-        <v>25</v>
-      </c>
-      <c r="O234" t="s">
-        <v>51</v>
-      </c>
       <c r="P234" t="s">
         <v>79</v>
       </c>
       <c r="Q234" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R234" t="s">
         <v>25</v>
@@ -14574,13 +14571,13 @@
         <v>35</v>
       </c>
       <c r="D235" t="s">
+        <v>324</v>
+      </c>
+      <c r="E235" t="s">
+        <v>22</v>
+      </c>
+      <c r="F235" t="s">
         <v>325</v>
-      </c>
-      <c r="E235" t="s">
-        <v>40</v>
-      </c>
-      <c r="F235" t="s">
-        <v>326</v>
       </c>
       <c r="G235" t="s">
         <v>24</v>
@@ -14607,13 +14604,13 @@
         <v>25</v>
       </c>
       <c r="O235" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P235" t="s">
         <v>79</v>
       </c>
       <c r="Q235" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R235" t="s">
         <v>25</v>
@@ -14630,13 +14627,13 @@
         <v>35</v>
       </c>
       <c r="D236" t="s">
+        <v>324</v>
+      </c>
+      <c r="E236" t="s">
+        <v>40</v>
+      </c>
+      <c r="F236" t="s">
         <v>325</v>
-      </c>
-      <c r="E236" t="s">
-        <v>22</v>
-      </c>
-      <c r="F236" t="s">
-        <v>326</v>
       </c>
       <c r="G236" t="s">
         <v>24</v>
@@ -14663,13 +14660,13 @@
         <v>25</v>
       </c>
       <c r="O236" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P236" t="s">
         <v>79</v>
       </c>
       <c r="Q236" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R236" t="s">
         <v>25</v>
@@ -14686,13 +14683,13 @@
         <v>35</v>
       </c>
       <c r="D237" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E237" t="s">
         <v>40</v>
       </c>
       <c r="F237" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G237" t="s">
         <v>24</v>
@@ -14710,22 +14707,22 @@
         <v>86</v>
       </c>
       <c r="L237" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="M237" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N237" t="s">
         <v>25</v>
       </c>
       <c r="O237" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="P237" t="s">
         <v>79</v>
       </c>
       <c r="Q237" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R237" t="s">
         <v>25</v>
@@ -14742,13 +14739,13 @@
         <v>35</v>
       </c>
       <c r="D238" t="s">
+        <v>324</v>
+      </c>
+      <c r="E238" t="s">
+        <v>35</v>
+      </c>
+      <c r="F238" t="s">
         <v>325</v>
-      </c>
-      <c r="E238" t="s">
-        <v>40</v>
-      </c>
-      <c r="F238" t="s">
-        <v>326</v>
       </c>
       <c r="G238" t="s">
         <v>24</v>
@@ -14775,13 +14772,13 @@
         <v>25</v>
       </c>
       <c r="O238" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P238" t="s">
         <v>79</v>
       </c>
       <c r="Q238" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R238" t="s">
         <v>25</v>
@@ -14798,13 +14795,13 @@
         <v>35</v>
       </c>
       <c r="D239" t="s">
+        <v>324</v>
+      </c>
+      <c r="E239" t="s">
+        <v>40</v>
+      </c>
+      <c r="F239" t="s">
         <v>325</v>
-      </c>
-      <c r="E239" t="s">
-        <v>35</v>
-      </c>
-      <c r="F239" t="s">
-        <v>326</v>
       </c>
       <c r="G239" t="s">
         <v>24</v>
@@ -14831,13 +14828,13 @@
         <v>25</v>
       </c>
       <c r="O239" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P239" t="s">
         <v>79</v>
       </c>
       <c r="Q239" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R239" t="s">
         <v>25</v>
@@ -14854,13 +14851,13 @@
         <v>35</v>
       </c>
       <c r="D240" t="s">
+        <v>324</v>
+      </c>
+      <c r="E240" t="s">
+        <v>22</v>
+      </c>
+      <c r="F240" t="s">
         <v>325</v>
-      </c>
-      <c r="E240" t="s">
-        <v>40</v>
-      </c>
-      <c r="F240" t="s">
-        <v>326</v>
       </c>
       <c r="G240" t="s">
         <v>24</v>
@@ -14872,28 +14869,28 @@
         <v>26</v>
       </c>
       <c r="J240" t="s">
+        <v>51</v>
+      </c>
+      <c r="K240" t="s">
+        <v>104</v>
+      </c>
+      <c r="L240" t="s">
+        <v>105</v>
+      </c>
+      <c r="M240" t="s">
+        <v>106</v>
+      </c>
+      <c r="N240" t="s">
+        <v>25</v>
+      </c>
+      <c r="O240" t="s">
         <v>42</v>
       </c>
-      <c r="K240" t="s">
-        <v>86</v>
-      </c>
-      <c r="L240" t="s">
-        <v>87</v>
-      </c>
-      <c r="M240" t="s">
-        <v>88</v>
-      </c>
-      <c r="N240" t="s">
-        <v>25</v>
-      </c>
-      <c r="O240" t="s">
-        <v>51</v>
-      </c>
       <c r="P240" t="s">
         <v>79</v>
       </c>
       <c r="Q240" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R240" t="s">
         <v>25</v>
@@ -14910,13 +14907,13 @@
         <v>35</v>
       </c>
       <c r="D241" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E241" t="s">
         <v>22</v>
       </c>
       <c r="F241" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G241" t="s">
         <v>24</v>
@@ -14943,13 +14940,13 @@
         <v>25</v>
       </c>
       <c r="O241" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P241" t="s">
         <v>79</v>
       </c>
       <c r="Q241" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R241" t="s">
         <v>25</v>
@@ -14966,13 +14963,13 @@
         <v>35</v>
       </c>
       <c r="D242" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E242" t="s">
         <v>22</v>
       </c>
       <c r="F242" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G242" t="s">
         <v>24</v>
@@ -14987,25 +14984,25 @@
         <v>51</v>
       </c>
       <c r="K242" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L242" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M242" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="N242" t="s">
         <v>25</v>
       </c>
       <c r="O242" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="P242" t="s">
         <v>79</v>
       </c>
       <c r="Q242" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R242" t="s">
         <v>25</v>
@@ -15022,13 +15019,13 @@
         <v>35</v>
       </c>
       <c r="D243" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E243" t="s">
         <v>22</v>
       </c>
       <c r="F243" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G243" t="s">
         <v>24</v>
@@ -15055,13 +15052,13 @@
         <v>25</v>
       </c>
       <c r="O243" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P243" t="s">
         <v>79</v>
       </c>
       <c r="Q243" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R243" t="s">
         <v>25</v>
@@ -15078,13 +15075,13 @@
         <v>35</v>
       </c>
       <c r="D244" t="s">
+        <v>324</v>
+      </c>
+      <c r="E244" t="s">
+        <v>40</v>
+      </c>
+      <c r="F244" t="s">
         <v>325</v>
-      </c>
-      <c r="E244" t="s">
-        <v>22</v>
-      </c>
-      <c r="F244" t="s">
-        <v>326</v>
       </c>
       <c r="G244" t="s">
         <v>24</v>
@@ -15111,13 +15108,13 @@
         <v>25</v>
       </c>
       <c r="O244" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P244" t="s">
         <v>79</v>
       </c>
       <c r="Q244" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R244" t="s">
         <v>25</v>
@@ -15131,57 +15128,57 @@
         <v>19</v>
       </c>
       <c r="C245" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D245" t="s">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="E245" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F245" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="G245" t="s">
-        <v>24</v>
+        <v>355</v>
       </c>
       <c r="H245" t="s">
         <v>78</v>
       </c>
       <c r="I245" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J245" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="K245" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="L245" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="M245" t="s">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="N245" t="s">
         <v>25</v>
       </c>
       <c r="O245" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="P245" t="s">
         <v>79</v>
       </c>
       <c r="Q245" t="s">
-        <v>326</v>
+        <v>25</v>
       </c>
       <c r="R245" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B246" t="s">
         <v>19</v>
@@ -15190,34 +15187,34 @@
         <v>19</v>
       </c>
       <c r="D246" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="E246" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="F246" t="s">
-        <v>355</v>
+        <v>122</v>
       </c>
       <c r="G246" t="s">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="H246" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="I246" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J246" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K246" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L246" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="M246" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="N246" t="s">
         <v>25</v>
@@ -15229,10 +15226,10 @@
         <v>79</v>
       </c>
       <c r="Q246" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="R246" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
     </row>
     <row r="247">
@@ -15264,16 +15261,16 @@
         <v>26</v>
       </c>
       <c r="J247" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="K247" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="L247" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="M247" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="N247" t="s">
         <v>25</v>
@@ -15305,7 +15302,7 @@
         <v>121</v>
       </c>
       <c r="E248" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F248" t="s">
         <v>122</v>
@@ -15320,16 +15317,16 @@
         <v>26</v>
       </c>
       <c r="J248" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K248" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L248" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="M248" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="N248" t="s">
         <v>25</v>
@@ -15361,7 +15358,7 @@
         <v>121</v>
       </c>
       <c r="E249" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="F249" t="s">
         <v>122</v>
@@ -15379,13 +15376,13 @@
         <v>51</v>
       </c>
       <c r="K249" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L249" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M249" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="N249" t="s">
         <v>25</v>
@@ -15417,7 +15414,7 @@
         <v>121</v>
       </c>
       <c r="E250" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F250" t="s">
         <v>122</v>
@@ -15426,22 +15423,22 @@
         <v>77</v>
       </c>
       <c r="H250" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="I250" t="s">
         <v>26</v>
       </c>
       <c r="J250" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="K250" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="L250" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="M250" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="N250" t="s">
         <v>25</v>
@@ -15488,16 +15485,16 @@
         <v>26</v>
       </c>
       <c r="J251" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="K251" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="L251" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="M251" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="N251" t="s">
         <v>25</v>
@@ -15529,7 +15526,7 @@
         <v>121</v>
       </c>
       <c r="E252" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F252" t="s">
         <v>122</v>
@@ -15544,16 +15541,16 @@
         <v>26</v>
       </c>
       <c r="J252" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K252" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="L252" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="M252" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="N252" t="s">
         <v>25</v>
@@ -15585,7 +15582,7 @@
         <v>121</v>
       </c>
       <c r="E253" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F253" t="s">
         <v>122</v>
@@ -15600,16 +15597,16 @@
         <v>26</v>
       </c>
       <c r="J253" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K253" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="L253" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="M253" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="N253" t="s">
         <v>25</v>
@@ -15638,7 +15635,7 @@
         <v>19</v>
       </c>
       <c r="D254" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="E254" t="s">
         <v>22</v>
@@ -15650,22 +15647,22 @@
         <v>77</v>
       </c>
       <c r="H254" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="I254" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="J254" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K254" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="L254" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="M254" t="s">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="N254" t="s">
         <v>25</v>
@@ -15674,7 +15671,7 @@
         <v>25</v>
       </c>
       <c r="P254" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="Q254" t="s">
         <v>122</v>
@@ -15706,13 +15703,13 @@
         <v>77</v>
       </c>
       <c r="H255" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="I255" t="s">
         <v>140</v>
       </c>
       <c r="J255" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K255" t="s">
         <v>25</v>
@@ -15753,7 +15750,7 @@
         <v>139</v>
       </c>
       <c r="E256" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F256" t="s">
         <v>122</v>
@@ -15768,7 +15765,7 @@
         <v>140</v>
       </c>
       <c r="J256" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="K256" t="s">
         <v>25</v>
@@ -15803,37 +15800,37 @@
         <v>19</v>
       </c>
       <c r="C257" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="D257" t="s">
-        <v>139</v>
+        <v>368</v>
       </c>
       <c r="E257" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F257" t="s">
-        <v>122</v>
+        <v>239</v>
       </c>
       <c r="G257" t="s">
         <v>77</v>
       </c>
       <c r="H257" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I257" t="s">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="J257" t="s">
         <v>42</v>
       </c>
       <c r="K257" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="L257" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="M257" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="N257" t="s">
         <v>25</v>
@@ -15842,18 +15839,18 @@
         <v>25</v>
       </c>
       <c r="P257" t="s">
-        <v>141</v>
+        <v>369</v>
       </c>
       <c r="Q257" t="s">
-        <v>122</v>
+        <v>240</v>
       </c>
       <c r="R257" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B258" t="s">
         <v>19</v>
@@ -15862,7 +15859,7 @@
         <v>59</v>
       </c>
       <c r="D258" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E258" t="s">
         <v>19</v>
@@ -15898,7 +15895,7 @@
         <v>25</v>
       </c>
       <c r="P258" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q258" t="s">
         <v>240</v>
@@ -15918,13 +15915,13 @@
         <v>59</v>
       </c>
       <c r="D259" t="s">
-        <v>369</v>
+        <v>302</v>
       </c>
       <c r="E259" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F259" t="s">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="G259" t="s">
         <v>77</v>
@@ -15936,16 +15933,16 @@
         <v>26</v>
       </c>
       <c r="J259" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K259" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L259" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="M259" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="N259" t="s">
         <v>25</v>
@@ -15954,68 +15951,12 @@
         <v>25</v>
       </c>
       <c r="P259" t="s">
-        <v>370</v>
+        <v>303</v>
       </c>
       <c r="Q259" t="s">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="R259" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>372</v>
-      </c>
-      <c r="B260" t="s">
-        <v>19</v>
-      </c>
-      <c r="C260" t="s">
-        <v>59</v>
-      </c>
-      <c r="D260" t="s">
-        <v>303</v>
-      </c>
-      <c r="E260" t="s">
-        <v>22</v>
-      </c>
-      <c r="F260" t="s">
-        <v>182</v>
-      </c>
-      <c r="G260" t="s">
-        <v>77</v>
-      </c>
-      <c r="H260" t="s">
-        <v>25</v>
-      </c>
-      <c r="I260" t="s">
-        <v>26</v>
-      </c>
-      <c r="J260" t="s">
-        <v>51</v>
-      </c>
-      <c r="K260" t="s">
-        <v>104</v>
-      </c>
-      <c r="L260" t="s">
-        <v>105</v>
-      </c>
-      <c r="M260" t="s">
-        <v>106</v>
-      </c>
-      <c r="N260" t="s">
-        <v>25</v>
-      </c>
-      <c r="O260" t="s">
-        <v>25</v>
-      </c>
-      <c r="P260" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q260" t="s">
-        <v>183</v>
-      </c>
-      <c r="R260" t="s">
         <v>183</v>
       </c>
     </row>
